--- a/train_data3.xlsx
+++ b/train_data3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="728">
   <si>
     <t>レースID</t>
   </si>
@@ -2177,6 +2177,27 @@
   </si>
   <si>
     <t>ショウナンハヤナミ</t>
+  </si>
+  <si>
+    <t>ダイシンピスケス</t>
+  </si>
+  <si>
+    <t>ギュルヴィ</t>
+  </si>
+  <si>
+    <t>ミッキークレスト</t>
+  </si>
+  <si>
+    <t>ダブルジョーク</t>
+  </si>
+  <si>
+    <t>マイノワール</t>
+  </si>
+  <si>
+    <t>リアレスト</t>
+  </si>
+  <si>
+    <t>カズタンジャー</t>
   </si>
 </sst>
 </file>
@@ -2184,10 +2205,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -2218,6 +2239,74 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2232,32 +2321,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2269,16 +2353,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2291,57 +2368,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2350,13 +2378,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2371,37 +2392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2413,55 +2404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2479,13 +2422,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2497,19 +2482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2521,37 +2494,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2631,30 +2652,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -2665,15 +2662,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2704,6 +2692,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -2718,16 +2739,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2736,127 +2757,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -2866,7 +2887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2903,12 +2924,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -3305,7 +3320,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1197"/>
+  <dimension ref="A1:O1213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" width="8.72222222222222" style="1"/>
@@ -49545,37 +49560,37 @@
       <c r="A1146" s="1">
         <v>78</v>
       </c>
-      <c r="B1146" s="15">
-        <v>1</v>
-      </c>
-      <c r="C1146" s="16" t="s">
+      <c r="B1146" s="13">
+        <v>1</v>
+      </c>
+      <c r="C1146" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="D1146" s="15">
+      <c r="D1146" s="13">
         <v>55</v>
       </c>
-      <c r="E1146" s="15">
+      <c r="E1146" s="13">
         <v>27.6</v>
       </c>
-      <c r="F1146" s="15">
+      <c r="F1146" s="13">
         <v>24</v>
       </c>
-      <c r="G1146" s="16">
+      <c r="G1146" s="14">
         <v>87</v>
       </c>
-      <c r="H1146" s="15">
+      <c r="H1146" s="13">
         <v>20</v>
       </c>
-      <c r="I1146" s="16">
+      <c r="I1146" s="14">
         <v>86</v>
       </c>
-      <c r="J1146" s="15">
+      <c r="J1146" s="13">
         <v>94</v>
       </c>
-      <c r="K1146" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1146" s="15">
+      <c r="K1146" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1146" s="13">
         <v>1</v>
       </c>
       <c r="M1146"/>
@@ -49590,37 +49605,37 @@
       <c r="A1147" s="1">
         <v>78</v>
       </c>
-      <c r="B1147" s="15">
+      <c r="B1147" s="13">
         <v>2</v>
       </c>
-      <c r="C1147" s="16" t="s">
+      <c r="C1147" s="14" t="s">
         <v>514</v>
       </c>
-      <c r="D1147" s="15">
+      <c r="D1147" s="13">
         <v>55</v>
       </c>
-      <c r="E1147" s="15">
+      <c r="E1147" s="13">
         <v>31.2</v>
       </c>
-      <c r="F1147" s="15">
+      <c r="F1147" s="13">
         <v>18</v>
       </c>
-      <c r="G1147" s="16">
+      <c r="G1147" s="14">
         <v>87</v>
       </c>
-      <c r="H1147" s="15">
+      <c r="H1147" s="13">
         <v>34</v>
       </c>
-      <c r="I1147" s="16">
+      <c r="I1147" s="14">
         <v>87</v>
       </c>
-      <c r="J1147" s="15">
+      <c r="J1147" s="13">
         <v>48</v>
       </c>
-      <c r="K1147" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1147" s="15">
+      <c r="K1147" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1147" s="13">
         <v>1</v>
       </c>
       <c r="M1147"/>
@@ -49635,31 +49650,31 @@
       <c r="A1148" s="1">
         <v>78</v>
       </c>
-      <c r="B1148" s="15">
+      <c r="B1148" s="13">
         <v>3</v>
       </c>
-      <c r="C1148" s="16" t="s">
+      <c r="C1148" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="D1148" s="15">
+      <c r="D1148" s="13">
         <v>55</v>
       </c>
-      <c r="E1148" s="15">
+      <c r="E1148" s="13">
         <v>6.3</v>
       </c>
-      <c r="F1148" s="15">
+      <c r="F1148" s="13">
         <v>14</v>
       </c>
-      <c r="G1148" s="16">
+      <c r="G1148" s="14">
         <v>80</v>
       </c>
-      <c r="H1148" s="15">
+      <c r="H1148" s="13">
         <v>-87</v>
       </c>
-      <c r="I1148" s="16">
+      <c r="I1148" s="14">
         <v>79</v>
       </c>
-      <c r="J1148" s="15">
+      <c r="J1148" s="13">
         <v>34</v>
       </c>
       <c r="K1148"/>
@@ -49676,31 +49691,31 @@
       <c r="A1149" s="1">
         <v>78</v>
       </c>
-      <c r="B1149" s="15">
+      <c r="B1149" s="13">
         <v>4</v>
       </c>
-      <c r="C1149" s="16" t="s">
+      <c r="C1149" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="D1149" s="15">
+      <c r="D1149" s="13">
         <v>55</v>
       </c>
-      <c r="E1149" s="15">
+      <c r="E1149" s="13">
         <v>10.8</v>
       </c>
-      <c r="F1149" s="15">
+      <c r="F1149" s="13">
         <v>18</v>
       </c>
-      <c r="G1149" s="16">
+      <c r="G1149" s="14">
         <v>93</v>
       </c>
-      <c r="H1149" s="15">
+      <c r="H1149" s="13">
         <v>65</v>
       </c>
-      <c r="I1149" s="16">
+      <c r="I1149" s="14">
         <v>86</v>
       </c>
-      <c r="J1149" s="15">
+      <c r="J1149" s="13">
         <v>46</v>
       </c>
       <c r="K1149"/>
@@ -49717,36 +49732,36 @@
       <c r="A1150" s="1">
         <v>78</v>
       </c>
-      <c r="B1150" s="15">
+      <c r="B1150" s="13">
         <v>5</v>
       </c>
-      <c r="C1150" s="16" t="s">
+      <c r="C1150" s="14" t="s">
         <v>704</v>
       </c>
-      <c r="D1150" s="15">
+      <c r="D1150" s="13">
         <v>55</v>
       </c>
-      <c r="E1150" s="15">
+      <c r="E1150" s="13">
         <v>13.4</v>
       </c>
-      <c r="F1150" s="15">
+      <c r="F1150" s="13">
         <v>17</v>
       </c>
-      <c r="G1150" s="16">
+      <c r="G1150" s="14">
         <v>88</v>
       </c>
-      <c r="H1150" s="15">
+      <c r="H1150" s="13">
         <v>37</v>
       </c>
-      <c r="I1150" s="16">
+      <c r="I1150" s="14">
         <v>69</v>
       </c>
-      <c r="J1150" s="15">
+      <c r="J1150" s="13">
         <v>95</v>
       </c>
       <c r="K1150"/>
       <c r="L1150"/>
-      <c r="M1150" s="15">
+      <c r="M1150" s="13">
         <v>1</v>
       </c>
       <c r="N1150" s="11">
@@ -49760,31 +49775,31 @@
       <c r="A1151" s="1">
         <v>78</v>
       </c>
-      <c r="B1151" s="15">
+      <c r="B1151" s="13">
         <v>6</v>
       </c>
-      <c r="C1151" s="16" t="s">
+      <c r="C1151" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="D1151" s="15">
+      <c r="D1151" s="13">
         <v>55</v>
       </c>
-      <c r="E1151" s="15">
+      <c r="E1151" s="13">
         <v>31.5</v>
       </c>
-      <c r="F1151" s="15">
+      <c r="F1151" s="13">
         <v>32</v>
       </c>
-      <c r="G1151" s="16">
+      <c r="G1151" s="14">
         <v>91</v>
       </c>
-      <c r="H1151" s="15">
+      <c r="H1151" s="13">
         <v>51</v>
       </c>
-      <c r="I1151" s="16">
+      <c r="I1151" s="14">
         <v>79</v>
       </c>
-      <c r="J1151" s="15">
+      <c r="J1151" s="13">
         <v>31</v>
       </c>
       <c r="K1151"/>
@@ -49801,36 +49816,36 @@
       <c r="A1152" s="1">
         <v>78</v>
       </c>
-      <c r="B1152" s="15">
+      <c r="B1152" s="13">
         <v>7</v>
       </c>
-      <c r="C1152" s="16" t="s">
+      <c r="C1152" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="D1152" s="15">
+      <c r="D1152" s="13">
         <v>55</v>
       </c>
-      <c r="E1152" s="15">
+      <c r="E1152" s="13">
         <v>65</v>
       </c>
-      <c r="F1152" s="15">
+      <c r="F1152" s="13">
         <v>54</v>
       </c>
-      <c r="G1152" s="16">
+      <c r="G1152" s="14">
         <v>93</v>
       </c>
-      <c r="H1152" s="15">
+      <c r="H1152" s="13">
         <v>68</v>
       </c>
-      <c r="I1152" s="16">
+      <c r="I1152" s="14">
         <v>86</v>
       </c>
-      <c r="J1152" s="15">
+      <c r="J1152" s="13">
         <v>60</v>
       </c>
       <c r="K1152"/>
       <c r="L1152"/>
-      <c r="M1152" s="15">
+      <c r="M1152" s="13">
         <v>1</v>
       </c>
       <c r="N1152" s="11">
@@ -49844,38 +49859,38 @@
       <c r="A1153" s="1">
         <v>78</v>
       </c>
-      <c r="B1153" s="15">
+      <c r="B1153" s="13">
         <v>8</v>
       </c>
-      <c r="C1153" s="16" t="s">
+      <c r="C1153" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="D1153" s="15">
+      <c r="D1153" s="13">
         <v>55</v>
       </c>
-      <c r="E1153" s="15">
+      <c r="E1153" s="13">
         <v>18.7</v>
       </c>
-      <c r="F1153" s="15">
+      <c r="F1153" s="13">
         <v>25</v>
       </c>
-      <c r="G1153" s="16">
+      <c r="G1153" s="14">
         <v>78</v>
       </c>
-      <c r="H1153" s="15">
+      <c r="H1153" s="13">
         <v>48</v>
       </c>
-      <c r="I1153" s="16">
+      <c r="I1153" s="14">
         <v>89</v>
       </c>
-      <c r="J1153" s="15">
+      <c r="J1153" s="13">
         <v>90</v>
       </c>
-      <c r="K1153" s="15">
+      <c r="K1153" s="13">
         <v>1</v>
       </c>
       <c r="L1153"/>
-      <c r="M1153" s="15">
+      <c r="M1153" s="13">
         <v>1</v>
       </c>
       <c r="N1153" s="11">
@@ -49889,36 +49904,36 @@
       <c r="A1154" s="1">
         <v>78</v>
       </c>
-      <c r="B1154" s="15">
+      <c r="B1154" s="13">
         <v>9</v>
       </c>
-      <c r="C1154" s="16" t="s">
+      <c r="C1154" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D1154" s="15">
+      <c r="D1154" s="13">
         <v>55</v>
       </c>
-      <c r="E1154" s="15">
+      <c r="E1154" s="13">
         <v>6.1</v>
       </c>
-      <c r="F1154" s="15">
+      <c r="F1154" s="13">
         <v>20</v>
       </c>
-      <c r="G1154" s="16">
+      <c r="G1154" s="14">
         <v>97</v>
       </c>
-      <c r="H1154" s="15">
+      <c r="H1154" s="13">
         <v>-91</v>
       </c>
-      <c r="I1154" s="16">
+      <c r="I1154" s="14">
         <v>105</v>
       </c>
-      <c r="J1154" s="15">
+      <c r="J1154" s="13">
         <v>23</v>
       </c>
       <c r="K1154"/>
       <c r="L1154"/>
-      <c r="M1154" s="15">
+      <c r="M1154" s="13">
         <v>1</v>
       </c>
       <c r="N1154" s="11">
@@ -49932,31 +49947,31 @@
       <c r="A1155" s="1">
         <v>78</v>
       </c>
-      <c r="B1155" s="15">
+      <c r="B1155" s="13">
         <v>10</v>
       </c>
-      <c r="C1155" s="16" t="s">
+      <c r="C1155" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D1155" s="15">
+      <c r="D1155" s="13">
         <v>55</v>
       </c>
-      <c r="E1155" s="15">
+      <c r="E1155" s="13">
         <v>27.3</v>
       </c>
-      <c r="F1155" s="15">
+      <c r="F1155" s="13">
         <v>26</v>
       </c>
-      <c r="G1155" s="16">
+      <c r="G1155" s="14">
         <v>88</v>
       </c>
-      <c r="H1155" s="15">
+      <c r="H1155" s="13">
         <v>40</v>
       </c>
-      <c r="I1155" s="16">
+      <c r="I1155" s="14">
         <v>98</v>
       </c>
-      <c r="J1155" s="15">
+      <c r="J1155" s="13">
         <v>-50</v>
       </c>
       <c r="K1155"/>
@@ -49973,31 +49988,31 @@
       <c r="A1156" s="1">
         <v>78</v>
       </c>
-      <c r="B1156" s="15">
+      <c r="B1156" s="13">
         <v>11</v>
       </c>
-      <c r="C1156" s="16" t="s">
+      <c r="C1156" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="D1156" s="15">
+      <c r="D1156" s="13">
         <v>55</v>
       </c>
-      <c r="E1156" s="15">
+      <c r="E1156" s="13">
         <v>21</v>
       </c>
-      <c r="F1156" s="15">
+      <c r="F1156" s="13">
         <v>26</v>
       </c>
-      <c r="G1156" s="16">
+      <c r="G1156" s="14">
         <v>78</v>
       </c>
-      <c r="H1156" s="15">
+      <c r="H1156" s="13">
         <v>25</v>
       </c>
-      <c r="I1156" s="16">
+      <c r="I1156" s="14">
         <v>88</v>
       </c>
-      <c r="J1156" s="15">
+      <c r="J1156" s="13">
         <v>46</v>
       </c>
       <c r="K1156"/>
@@ -50014,31 +50029,31 @@
       <c r="A1157" s="1">
         <v>78</v>
       </c>
-      <c r="B1157" s="15">
+      <c r="B1157" s="13">
         <v>12</v>
       </c>
-      <c r="C1157" s="16" t="s">
+      <c r="C1157" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D1157" s="15">
+      <c r="D1157" s="13">
         <v>55</v>
       </c>
-      <c r="E1157" s="15">
+      <c r="E1157" s="13">
         <v>41.1</v>
       </c>
-      <c r="F1157" s="15">
+      <c r="F1157" s="13">
         <v>28</v>
       </c>
-      <c r="G1157" s="16">
+      <c r="G1157" s="14">
         <v>87</v>
       </c>
-      <c r="H1157" s="15">
+      <c r="H1157" s="13">
         <v>46</v>
       </c>
-      <c r="I1157" s="16">
+      <c r="I1157" s="14">
         <v>96</v>
       </c>
-      <c r="J1157" s="15">
+      <c r="J1157" s="13">
         <v>72</v>
       </c>
       <c r="K1157"/>
@@ -50055,36 +50070,36 @@
       <c r="A1158" s="1">
         <v>79</v>
       </c>
-      <c r="B1158" s="15">
-        <v>1</v>
-      </c>
-      <c r="C1158" s="16" t="s">
+      <c r="B1158" s="13">
+        <v>1</v>
+      </c>
+      <c r="C1158" s="14" t="s">
         <v>707</v>
       </c>
-      <c r="D1158" s="15">
+      <c r="D1158" s="13">
         <v>57</v>
       </c>
-      <c r="E1158" s="15">
+      <c r="E1158" s="13">
         <v>5.9</v>
       </c>
-      <c r="F1158" s="15">
+      <c r="F1158" s="13">
         <v>20</v>
       </c>
-      <c r="G1158" s="16">
+      <c r="G1158" s="14">
         <v>79</v>
       </c>
-      <c r="H1158" s="15">
+      <c r="H1158" s="13">
         <v>-25</v>
       </c>
-      <c r="I1158" s="16">
+      <c r="I1158" s="14">
         <v>87</v>
       </c>
-      <c r="J1158" s="15">
+      <c r="J1158" s="13">
         <v>24</v>
       </c>
       <c r="K1158"/>
       <c r="L1158"/>
-      <c r="M1158" s="15">
+      <c r="M1158" s="13">
         <v>1</v>
       </c>
       <c r="N1158" s="11">
@@ -50098,31 +50113,31 @@
       <c r="A1159" s="1">
         <v>79</v>
       </c>
-      <c r="B1159" s="15">
+      <c r="B1159" s="13">
         <v>2</v>
       </c>
-      <c r="C1159" s="16" t="s">
+      <c r="C1159" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D1159" s="15">
+      <c r="D1159" s="13">
         <v>57</v>
       </c>
-      <c r="E1159" s="15">
+      <c r="E1159" s="13">
         <v>14.4</v>
       </c>
-      <c r="F1159" s="15">
+      <c r="F1159" s="13">
         <v>18</v>
       </c>
-      <c r="G1159" s="16">
+      <c r="G1159" s="14">
         <v>103</v>
       </c>
-      <c r="H1159" s="15">
+      <c r="H1159" s="13">
         <v>38</v>
       </c>
-      <c r="I1159" s="16">
+      <c r="I1159" s="14">
         <v>97</v>
       </c>
-      <c r="J1159" s="15">
+      <c r="J1159" s="13">
         <v>42</v>
       </c>
       <c r="K1159"/>
@@ -50139,37 +50154,37 @@
       <c r="A1160" s="1">
         <v>79</v>
       </c>
-      <c r="B1160" s="15">
+      <c r="B1160" s="13">
         <v>3</v>
       </c>
-      <c r="C1160" s="16" t="s">
+      <c r="C1160" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="D1160" s="15">
+      <c r="D1160" s="13">
         <v>57</v>
       </c>
-      <c r="E1160" s="15">
+      <c r="E1160" s="13">
         <v>9.7</v>
       </c>
-      <c r="F1160" s="15">
+      <c r="F1160" s="13">
         <v>14</v>
       </c>
-      <c r="G1160" s="16">
+      <c r="G1160" s="14">
         <v>101</v>
       </c>
-      <c r="H1160" s="15">
+      <c r="H1160" s="13">
         <v>25</v>
       </c>
-      <c r="I1160" s="16">
+      <c r="I1160" s="14">
         <v>105</v>
       </c>
-      <c r="J1160" s="15">
+      <c r="J1160" s="13">
         <v>-15</v>
       </c>
-      <c r="K1160" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1160" s="15">
+      <c r="K1160" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1160" s="13">
         <v>1</v>
       </c>
       <c r="M1160"/>
@@ -50184,38 +50199,38 @@
       <c r="A1161" s="1">
         <v>79</v>
       </c>
-      <c r="B1161" s="15">
+      <c r="B1161" s="13">
         <v>4</v>
       </c>
-      <c r="C1161" s="16" t="s">
+      <c r="C1161" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="D1161" s="15">
+      <c r="D1161" s="13">
         <v>57</v>
       </c>
-      <c r="E1161" s="15">
+      <c r="E1161" s="13">
         <v>12.2</v>
       </c>
-      <c r="F1161" s="15">
+      <c r="F1161" s="13">
         <v>20</v>
       </c>
-      <c r="G1161" s="16">
+      <c r="G1161" s="14">
         <v>102</v>
       </c>
-      <c r="H1161" s="15">
+      <c r="H1161" s="13">
         <v>24</v>
       </c>
-      <c r="I1161" s="16">
+      <c r="I1161" s="14">
         <v>97</v>
       </c>
-      <c r="J1161" s="15">
+      <c r="J1161" s="13">
         <v>37</v>
       </c>
-      <c r="K1161" s="15">
+      <c r="K1161" s="13">
         <v>1</v>
       </c>
       <c r="L1161"/>
-      <c r="M1161" s="15">
+      <c r="M1161" s="13">
         <v>1</v>
       </c>
       <c r="N1161" s="11">
@@ -50229,35 +50244,35 @@
       <c r="A1162" s="1">
         <v>79</v>
       </c>
-      <c r="B1162" s="15">
+      <c r="B1162" s="13">
         <v>5</v>
       </c>
-      <c r="C1162" s="16" t="s">
+      <c r="C1162" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D1162" s="15">
+      <c r="D1162" s="13">
         <v>57</v>
       </c>
-      <c r="E1162" s="15">
+      <c r="E1162" s="13">
         <v>40.5</v>
       </c>
-      <c r="F1162" s="15">
+      <c r="F1162" s="13">
         <v>33</v>
       </c>
-      <c r="G1162" s="16">
+      <c r="G1162" s="14">
         <v>103</v>
       </c>
-      <c r="H1162" s="15">
+      <c r="H1162" s="13">
         <v>7</v>
       </c>
-      <c r="I1162" s="16">
+      <c r="I1162" s="14">
         <v>109</v>
       </c>
-      <c r="J1162" s="15">
+      <c r="J1162" s="13">
         <v>31</v>
       </c>
       <c r="K1162"/>
-      <c r="L1162" s="15">
+      <c r="L1162" s="13">
         <v>1</v>
       </c>
       <c r="M1162"/>
@@ -50272,40 +50287,40 @@
       <c r="A1163" s="1">
         <v>79</v>
       </c>
-      <c r="B1163" s="15">
+      <c r="B1163" s="13">
         <v>6</v>
       </c>
-      <c r="C1163" s="16" t="s">
+      <c r="C1163" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="D1163" s="15">
+      <c r="D1163" s="13">
         <v>57</v>
       </c>
-      <c r="E1163" s="15">
+      <c r="E1163" s="13">
         <v>46.8</v>
       </c>
-      <c r="F1163" s="15">
+      <c r="F1163" s="13">
         <v>40</v>
       </c>
-      <c r="G1163" s="16">
+      <c r="G1163" s="14">
         <v>107</v>
       </c>
-      <c r="H1163" s="15">
+      <c r="H1163" s="13">
         <v>59</v>
       </c>
-      <c r="I1163" s="16">
+      <c r="I1163" s="14">
         <v>88</v>
       </c>
-      <c r="J1163" s="15">
+      <c r="J1163" s="13">
         <v>33</v>
       </c>
-      <c r="K1163" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1163" s="15">
-        <v>1</v>
-      </c>
-      <c r="M1163" s="15">
+      <c r="K1163" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1163" s="13">
+        <v>1</v>
+      </c>
+      <c r="M1163" s="13">
         <v>1</v>
       </c>
       <c r="N1163" s="11">
@@ -50319,36 +50334,36 @@
       <c r="A1164" s="1">
         <v>79</v>
       </c>
-      <c r="B1164" s="15">
+      <c r="B1164" s="13">
         <v>7</v>
       </c>
-      <c r="C1164" s="16" t="s">
+      <c r="C1164" s="14" t="s">
         <v>708</v>
       </c>
-      <c r="D1164" s="15">
+      <c r="D1164" s="13">
         <v>57</v>
       </c>
-      <c r="E1164" s="15">
+      <c r="E1164" s="13">
         <v>6.4</v>
       </c>
-      <c r="F1164" s="15">
+      <c r="F1164" s="13">
         <v>24</v>
       </c>
-      <c r="G1164" s="16">
+      <c r="G1164" s="14">
         <v>80</v>
       </c>
-      <c r="H1164" s="15">
+      <c r="H1164" s="13">
         <v>39</v>
       </c>
-      <c r="I1164" s="16">
+      <c r="I1164" s="14">
         <v>95</v>
       </c>
-      <c r="J1164" s="15">
+      <c r="J1164" s="13">
         <v>84</v>
       </c>
       <c r="K1164"/>
       <c r="L1164"/>
-      <c r="M1164" s="15">
+      <c r="M1164" s="13">
         <v>1</v>
       </c>
       <c r="N1164" s="11">
@@ -50362,31 +50377,31 @@
       <c r="A1165" s="1">
         <v>79</v>
       </c>
-      <c r="B1165" s="15">
+      <c r="B1165" s="13">
         <v>8</v>
       </c>
-      <c r="C1165" s="16" t="s">
+      <c r="C1165" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D1165" s="15">
+      <c r="D1165" s="13">
         <v>57</v>
       </c>
-      <c r="E1165" s="15">
+      <c r="E1165" s="13">
         <v>42.5</v>
       </c>
-      <c r="F1165" s="15">
+      <c r="F1165" s="13">
         <v>32</v>
       </c>
-      <c r="G1165" s="16">
+      <c r="G1165" s="14">
         <v>106</v>
       </c>
-      <c r="H1165" s="15">
+      <c r="H1165" s="13">
         <v>81</v>
       </c>
-      <c r="I1165" s="16">
+      <c r="I1165" s="14">
         <v>105</v>
       </c>
-      <c r="J1165" s="15">
+      <c r="J1165" s="13">
         <v>113</v>
       </c>
       <c r="K1165"/>
@@ -50403,31 +50418,31 @@
       <c r="A1166" s="1">
         <v>79</v>
       </c>
-      <c r="B1166" s="15">
+      <c r="B1166" s="13">
         <v>9</v>
       </c>
-      <c r="C1166" s="16" t="s">
+      <c r="C1166" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D1166" s="15">
+      <c r="D1166" s="13">
         <v>57</v>
       </c>
-      <c r="E1166" s="15">
+      <c r="E1166" s="13">
         <v>37.2</v>
       </c>
-      <c r="F1166" s="15">
+      <c r="F1166" s="13">
         <v>32</v>
       </c>
-      <c r="G1166" s="16">
+      <c r="G1166" s="14">
         <v>104</v>
       </c>
-      <c r="H1166" s="15">
+      <c r="H1166" s="13">
         <v>64</v>
       </c>
-      <c r="I1166" s="16">
+      <c r="I1166" s="14">
         <v>105</v>
       </c>
-      <c r="J1166" s="15">
+      <c r="J1166" s="13">
         <v>4</v>
       </c>
       <c r="K1166"/>
@@ -50444,35 +50459,35 @@
       <c r="A1167" s="1">
         <v>79</v>
       </c>
-      <c r="B1167" s="15">
+      <c r="B1167" s="13">
         <v>10</v>
       </c>
-      <c r="C1167" s="16" t="s">
+      <c r="C1167" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="D1167" s="15">
+      <c r="D1167" s="13">
         <v>57</v>
       </c>
-      <c r="E1167" s="15">
+      <c r="E1167" s="13">
         <v>39.3</v>
       </c>
-      <c r="F1167" s="15">
+      <c r="F1167" s="13">
         <v>41</v>
       </c>
-      <c r="G1167" s="16">
+      <c r="G1167" s="14">
         <v>107</v>
       </c>
-      <c r="H1167" s="15">
+      <c r="H1167" s="13">
         <v>37</v>
       </c>
-      <c r="I1167" s="16">
+      <c r="I1167" s="14">
         <v>103</v>
       </c>
-      <c r="J1167" s="15">
+      <c r="J1167" s="13">
         <v>7</v>
       </c>
       <c r="K1167"/>
-      <c r="L1167" s="15">
+      <c r="L1167" s="13">
         <v>1</v>
       </c>
       <c r="M1167"/>
@@ -50487,36 +50502,36 @@
       <c r="A1168" s="1">
         <v>79</v>
       </c>
-      <c r="B1168" s="15">
+      <c r="B1168" s="13">
         <v>11</v>
       </c>
-      <c r="C1168" s="16" t="s">
+      <c r="C1168" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D1168" s="15">
+      <c r="D1168" s="13">
         <v>57</v>
       </c>
-      <c r="E1168" s="15">
+      <c r="E1168" s="13">
         <v>5.2</v>
       </c>
-      <c r="F1168" s="15">
+      <c r="F1168" s="13">
         <v>23</v>
       </c>
-      <c r="G1168" s="16">
+      <c r="G1168" s="14">
         <v>93</v>
       </c>
-      <c r="H1168" s="15">
+      <c r="H1168" s="13">
         <v>76</v>
       </c>
-      <c r="I1168" s="16">
+      <c r="I1168" s="14">
         <v>96</v>
       </c>
-      <c r="J1168" s="15">
+      <c r="J1168" s="13">
         <v>54</v>
       </c>
       <c r="K1168"/>
       <c r="L1168"/>
-      <c r="M1168" s="15">
+      <c r="M1168" s="13">
         <v>1</v>
       </c>
       <c r="N1168" s="11">
@@ -50530,31 +50545,31 @@
       <c r="A1169" s="1">
         <v>79</v>
       </c>
-      <c r="B1169" s="15">
+      <c r="B1169" s="13">
         <v>12</v>
       </c>
-      <c r="C1169" s="16" t="s">
+      <c r="C1169" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="D1169" s="15">
+      <c r="D1169" s="13">
         <v>57</v>
       </c>
-      <c r="E1169" s="15">
+      <c r="E1169" s="13">
         <v>7.4</v>
       </c>
-      <c r="F1169" s="15">
+      <c r="F1169" s="13">
         <v>23</v>
       </c>
-      <c r="G1169" s="16">
+      <c r="G1169" s="14">
         <v>106</v>
       </c>
-      <c r="H1169" s="15">
+      <c r="H1169" s="13">
         <v>18</v>
       </c>
-      <c r="I1169" s="16">
+      <c r="I1169" s="14">
         <v>99</v>
       </c>
-      <c r="J1169" s="15">
+      <c r="J1169" s="13">
         <v>23</v>
       </c>
       <c r="K1169"/>
@@ -50571,36 +50586,36 @@
       <c r="A1170" s="1">
         <v>79</v>
       </c>
-      <c r="B1170" s="15">
+      <c r="B1170" s="13">
         <v>13</v>
       </c>
-      <c r="C1170" s="16" t="s">
+      <c r="C1170" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="D1170" s="15">
+      <c r="D1170" s="13">
         <v>57</v>
       </c>
-      <c r="E1170" s="15">
+      <c r="E1170" s="13">
         <v>7</v>
       </c>
-      <c r="F1170" s="15">
+      <c r="F1170" s="13">
         <v>18</v>
       </c>
-      <c r="G1170" s="16">
+      <c r="G1170" s="14">
         <v>83</v>
       </c>
-      <c r="H1170" s="15">
+      <c r="H1170" s="13">
         <v>69</v>
       </c>
-      <c r="I1170" s="16">
+      <c r="I1170" s="14">
         <v>90</v>
       </c>
-      <c r="J1170" s="15">
+      <c r="J1170" s="13">
         <v>20</v>
       </c>
       <c r="K1170"/>
       <c r="L1170"/>
-      <c r="M1170" s="15">
+      <c r="M1170" s="13">
         <v>1</v>
       </c>
       <c r="N1170" s="11">
@@ -50614,31 +50629,31 @@
       <c r="A1171" s="1">
         <v>79</v>
       </c>
-      <c r="B1171" s="15">
+      <c r="B1171" s="13">
         <v>14</v>
       </c>
-      <c r="C1171" s="16" t="s">
+      <c r="C1171" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="D1171" s="15">
+      <c r="D1171" s="13">
         <v>57</v>
       </c>
-      <c r="E1171" s="15">
+      <c r="E1171" s="13">
         <v>5.2</v>
       </c>
-      <c r="F1171" s="15">
+      <c r="F1171" s="13">
         <v>16</v>
       </c>
-      <c r="G1171" s="16">
+      <c r="G1171" s="14">
         <v>73</v>
       </c>
-      <c r="H1171" s="15">
+      <c r="H1171" s="13">
         <v>-4</v>
       </c>
-      <c r="I1171" s="16">
+      <c r="I1171" s="14">
         <v>105</v>
       </c>
-      <c r="J1171" s="15">
+      <c r="J1171" s="13">
         <v>-33</v>
       </c>
       <c r="K1171"/>
@@ -50655,31 +50670,31 @@
       <c r="A1172" s="1">
         <v>79</v>
       </c>
-      <c r="B1172" s="15">
+      <c r="B1172" s="13">
         <v>15</v>
       </c>
-      <c r="C1172" s="16" t="s">
+      <c r="C1172" s="14" t="s">
         <v>710</v>
       </c>
-      <c r="D1172" s="15">
+      <c r="D1172" s="13">
         <v>57</v>
       </c>
-      <c r="E1172" s="15">
+      <c r="E1172" s="13">
         <v>10.3</v>
       </c>
-      <c r="F1172" s="15">
+      <c r="F1172" s="13">
         <v>24</v>
       </c>
-      <c r="G1172" s="16">
+      <c r="G1172" s="14">
         <v>97</v>
       </c>
-      <c r="H1172" s="15">
+      <c r="H1172" s="13">
         <v>56</v>
       </c>
-      <c r="I1172" s="16">
+      <c r="I1172" s="14">
         <v>92</v>
       </c>
-      <c r="J1172" s="15">
+      <c r="J1172" s="13">
         <v>67</v>
       </c>
       <c r="K1172"/>
@@ -50696,31 +50711,31 @@
       <c r="A1173" s="1">
         <v>79</v>
       </c>
-      <c r="B1173" s="15">
+      <c r="B1173" s="13">
         <v>16</v>
       </c>
-      <c r="C1173" s="16" t="s">
+      <c r="C1173" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="D1173" s="15">
+      <c r="D1173" s="13">
         <v>57</v>
       </c>
-      <c r="E1173" s="15">
+      <c r="E1173" s="13">
         <v>9.8</v>
       </c>
-      <c r="F1173" s="15">
+      <c r="F1173" s="13">
         <v>27</v>
       </c>
-      <c r="G1173" s="16">
+      <c r="G1173" s="14">
         <v>112</v>
       </c>
-      <c r="H1173" s="15">
+      <c r="H1173" s="13">
         <v>52</v>
       </c>
-      <c r="I1173" s="16">
+      <c r="I1173" s="14">
         <v>93</v>
       </c>
-      <c r="J1173" s="15">
+      <c r="J1173" s="13">
         <v>33</v>
       </c>
       <c r="K1173"/>
@@ -50737,34 +50752,34 @@
       <c r="A1174" s="1">
         <v>80</v>
       </c>
-      <c r="B1174" s="15">
-        <v>1</v>
-      </c>
-      <c r="C1174" s="16" t="s">
+      <c r="B1174" s="13">
+        <v>1</v>
+      </c>
+      <c r="C1174" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="D1174" s="15">
+      <c r="D1174" s="13">
         <v>57</v>
       </c>
-      <c r="E1174" s="15">
+      <c r="E1174" s="13">
         <v>19.1</v>
       </c>
-      <c r="F1174" s="15">
+      <c r="F1174" s="13">
         <v>19</v>
       </c>
-      <c r="G1174" s="16">
+      <c r="G1174" s="14">
         <v>98</v>
       </c>
-      <c r="H1174" s="15">
+      <c r="H1174" s="13">
         <v>26</v>
       </c>
-      <c r="I1174" s="16">
+      <c r="I1174" s="14">
         <v>95</v>
       </c>
-      <c r="J1174" s="15">
+      <c r="J1174" s="13">
         <v>-5</v>
       </c>
-      <c r="K1174" s="15">
+      <c r="K1174" s="13">
         <v>1</v>
       </c>
       <c r="L1174"/>
@@ -50780,31 +50795,31 @@
       <c r="A1175" s="1">
         <v>80</v>
       </c>
-      <c r="B1175" s="15">
+      <c r="B1175" s="13">
         <v>2</v>
       </c>
-      <c r="C1175" s="16" t="s">
+      <c r="C1175" s="14" t="s">
         <v>712</v>
       </c>
-      <c r="D1175" s="15">
+      <c r="D1175" s="13">
         <v>57</v>
       </c>
-      <c r="E1175" s="15">
+      <c r="E1175" s="13">
         <v>8.3</v>
       </c>
-      <c r="F1175" s="15">
+      <c r="F1175" s="13">
         <v>8</v>
       </c>
-      <c r="G1175" s="16">
+      <c r="G1175" s="14">
         <v>90</v>
       </c>
-      <c r="H1175" s="15">
+      <c r="H1175" s="13">
         <v>-77</v>
       </c>
-      <c r="I1175" s="16">
+      <c r="I1175" s="14">
         <v>97</v>
       </c>
-      <c r="J1175" s="15">
+      <c r="J1175" s="13">
         <v>-13</v>
       </c>
       <c r="K1175"/>
@@ -50821,38 +50836,38 @@
       <c r="A1176" s="1">
         <v>80</v>
       </c>
-      <c r="B1176" s="15">
+      <c r="B1176" s="13">
         <v>3</v>
       </c>
-      <c r="C1176" s="16" t="s">
+      <c r="C1176" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D1176" s="15">
+      <c r="D1176" s="13">
         <v>57</v>
       </c>
-      <c r="E1176" s="15">
+      <c r="E1176" s="13">
         <v>10.8</v>
       </c>
-      <c r="F1176" s="15">
+      <c r="F1176" s="13">
         <v>12</v>
       </c>
-      <c r="G1176" s="16">
+      <c r="G1176" s="14">
         <v>92</v>
       </c>
-      <c r="H1176" s="15">
+      <c r="H1176" s="13">
         <v>16</v>
       </c>
-      <c r="I1176" s="16">
+      <c r="I1176" s="14">
         <v>97</v>
       </c>
-      <c r="J1176" s="15">
+      <c r="J1176" s="13">
         <v>-69</v>
       </c>
       <c r="K1176"/>
-      <c r="L1176" s="15">
-        <v>1</v>
-      </c>
-      <c r="M1176" s="15">
+      <c r="L1176" s="13">
+        <v>1</v>
+      </c>
+      <c r="M1176" s="13">
         <v>1</v>
       </c>
       <c r="N1176" s="11">
@@ -50866,35 +50881,35 @@
       <c r="A1177" s="1">
         <v>80</v>
       </c>
-      <c r="B1177" s="15">
+      <c r="B1177" s="13">
         <v>4</v>
       </c>
-      <c r="C1177" s="16" t="s">
+      <c r="C1177" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="D1177" s="15">
+      <c r="D1177" s="13">
         <v>55</v>
       </c>
-      <c r="E1177" s="15">
+      <c r="E1177" s="13">
         <v>33</v>
       </c>
-      <c r="F1177" s="15">
+      <c r="F1177" s="13">
         <v>25</v>
       </c>
-      <c r="G1177" s="16">
+      <c r="G1177" s="14">
         <v>106</v>
       </c>
-      <c r="H1177" s="15">
+      <c r="H1177" s="13">
         <v>36</v>
       </c>
-      <c r="I1177" s="16">
+      <c r="I1177" s="14">
         <v>104</v>
       </c>
-      <c r="J1177" s="15">
+      <c r="J1177" s="13">
         <v>77</v>
       </c>
       <c r="K1177"/>
-      <c r="L1177" s="15">
+      <c r="L1177" s="13">
         <v>1</v>
       </c>
       <c r="M1177"/>
@@ -50909,31 +50924,31 @@
       <c r="A1178" s="1">
         <v>80</v>
       </c>
-      <c r="B1178" s="15">
+      <c r="B1178" s="13">
         <v>5</v>
       </c>
-      <c r="C1178" s="16" t="s">
+      <c r="C1178" s="14" t="s">
         <v>713</v>
       </c>
-      <c r="D1178" s="15">
+      <c r="D1178" s="13">
         <v>57</v>
       </c>
-      <c r="E1178" s="15">
+      <c r="E1178" s="13">
         <v>5.8</v>
       </c>
-      <c r="F1178" s="15">
+      <c r="F1178" s="13">
         <v>3</v>
       </c>
-      <c r="G1178" s="16">
+      <c r="G1178" s="14">
         <v>83</v>
       </c>
-      <c r="H1178" s="15">
+      <c r="H1178" s="13">
         <v>-56</v>
       </c>
-      <c r="I1178" s="16">
+      <c r="I1178" s="14">
         <v>77</v>
       </c>
-      <c r="J1178" s="15">
+      <c r="J1178" s="13">
         <v>-122</v>
       </c>
       <c r="K1178"/>
@@ -50950,34 +50965,34 @@
       <c r="A1179" s="1">
         <v>80</v>
       </c>
-      <c r="B1179" s="15">
+      <c r="B1179" s="13">
         <v>6</v>
       </c>
-      <c r="C1179" s="16" t="s">
+      <c r="C1179" s="14" t="s">
         <v>714</v>
       </c>
-      <c r="D1179" s="15">
+      <c r="D1179" s="13">
         <v>57</v>
       </c>
-      <c r="E1179" s="15">
+      <c r="E1179" s="13">
         <v>22.1</v>
       </c>
-      <c r="F1179" s="15">
+      <c r="F1179" s="13">
         <v>22</v>
       </c>
-      <c r="G1179" s="16">
+      <c r="G1179" s="14">
         <v>100</v>
       </c>
-      <c r="H1179" s="15">
+      <c r="H1179" s="13">
         <v>54</v>
       </c>
-      <c r="I1179" s="16">
+      <c r="I1179" s="14">
         <v>96</v>
       </c>
-      <c r="J1179" s="15">
+      <c r="J1179" s="13">
         <v>-31</v>
       </c>
-      <c r="K1179" s="15">
+      <c r="K1179" s="13">
         <v>1</v>
       </c>
       <c r="L1179"/>
@@ -50993,34 +51008,34 @@
       <c r="A1180" s="1">
         <v>80</v>
       </c>
-      <c r="B1180" s="15">
+      <c r="B1180" s="13">
         <v>7</v>
       </c>
-      <c r="C1180" s="16" t="s">
+      <c r="C1180" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="D1180" s="15">
+      <c r="D1180" s="13">
         <v>56</v>
       </c>
-      <c r="E1180" s="15">
+      <c r="E1180" s="13">
         <v>74.3</v>
       </c>
-      <c r="F1180" s="15">
+      <c r="F1180" s="13">
         <v>53</v>
       </c>
-      <c r="G1180" s="16">
+      <c r="G1180" s="14">
         <v>87</v>
       </c>
-      <c r="H1180" s="15">
+      <c r="H1180" s="13">
         <v>-39</v>
       </c>
-      <c r="I1180" s="16">
+      <c r="I1180" s="14">
         <v>108</v>
       </c>
-      <c r="J1180" s="15">
+      <c r="J1180" s="13">
         <v>38</v>
       </c>
-      <c r="K1180" s="15">
+      <c r="K1180" s="13">
         <v>1</v>
       </c>
       <c r="L1180"/>
@@ -51036,36 +51051,36 @@
       <c r="A1181" s="1">
         <v>80</v>
       </c>
-      <c r="B1181" s="15">
+      <c r="B1181" s="13">
         <v>8</v>
       </c>
-      <c r="C1181" s="16" t="s">
+      <c r="C1181" s="14" t="s">
         <v>715</v>
       </c>
-      <c r="D1181" s="15">
+      <c r="D1181" s="13">
         <v>57</v>
       </c>
-      <c r="E1181" s="15">
+      <c r="E1181" s="13">
         <v>6.7</v>
       </c>
-      <c r="F1181" s="15">
+      <c r="F1181" s="13">
         <v>6</v>
       </c>
-      <c r="G1181" s="16">
+      <c r="G1181" s="14">
         <v>88</v>
       </c>
-      <c r="H1181" s="15">
+      <c r="H1181" s="13">
         <v>45</v>
       </c>
-      <c r="I1181" s="16">
+      <c r="I1181" s="14">
         <v>88</v>
       </c>
-      <c r="J1181" s="15">
+      <c r="J1181" s="13">
         <v>45</v>
       </c>
       <c r="K1181"/>
       <c r="L1181"/>
-      <c r="M1181" s="15">
+      <c r="M1181" s="13">
         <v>1</v>
       </c>
       <c r="N1181" s="11">
@@ -51079,38 +51094,38 @@
       <c r="A1182" s="1">
         <v>80</v>
       </c>
-      <c r="B1182" s="15">
+      <c r="B1182" s="13">
         <v>9</v>
       </c>
-      <c r="C1182" s="16" t="s">
+      <c r="C1182" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D1182" s="15">
+      <c r="D1182" s="13">
         <v>57</v>
       </c>
-      <c r="E1182" s="15">
+      <c r="E1182" s="13">
         <v>63.5</v>
       </c>
-      <c r="F1182" s="15">
+      <c r="F1182" s="13">
         <v>43</v>
       </c>
-      <c r="G1182" s="16">
+      <c r="G1182" s="14">
         <v>96</v>
       </c>
-      <c r="H1182" s="15">
+      <c r="H1182" s="13">
         <v>28</v>
       </c>
-      <c r="I1182" s="16">
+      <c r="I1182" s="14">
         <v>103</v>
       </c>
-      <c r="J1182" s="15">
+      <c r="J1182" s="13">
         <v>9</v>
       </c>
       <c r="K1182"/>
-      <c r="L1182" s="15">
-        <v>1</v>
-      </c>
-      <c r="M1182" s="15">
+      <c r="L1182" s="13">
+        <v>1</v>
+      </c>
+      <c r="M1182" s="13">
         <v>1</v>
       </c>
       <c r="N1182" s="11">
@@ -51124,31 +51139,31 @@
       <c r="A1183" s="1">
         <v>80</v>
       </c>
-      <c r="B1183" s="15">
+      <c r="B1183" s="13">
         <v>10</v>
       </c>
-      <c r="C1183" s="16" t="s">
+      <c r="C1183" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="D1183" s="15">
+      <c r="D1183" s="13">
         <v>57</v>
       </c>
-      <c r="E1183" s="15">
+      <c r="E1183" s="13">
         <v>3.9</v>
       </c>
-      <c r="F1183" s="15">
+      <c r="F1183" s="13">
         <v>2</v>
       </c>
-      <c r="G1183" s="16">
+      <c r="G1183" s="14">
         <v>77</v>
       </c>
-      <c r="H1183" s="15">
+      <c r="H1183" s="13">
         <v>-139</v>
       </c>
-      <c r="I1183" s="16">
+      <c r="I1183" s="14">
         <v>82</v>
       </c>
-      <c r="J1183" s="15">
+      <c r="J1183" s="13">
         <v>-81</v>
       </c>
       <c r="K1183"/>
@@ -51165,36 +51180,36 @@
       <c r="A1184" s="1">
         <v>80</v>
       </c>
-      <c r="B1184" s="15">
+      <c r="B1184" s="13">
         <v>11</v>
       </c>
-      <c r="C1184" s="16" t="s">
+      <c r="C1184" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="D1184" s="15">
+      <c r="D1184" s="13">
         <v>57</v>
       </c>
-      <c r="E1184" s="15">
+      <c r="E1184" s="13">
         <v>9.8</v>
       </c>
-      <c r="F1184" s="15">
+      <c r="F1184" s="13">
         <v>2</v>
       </c>
-      <c r="G1184" s="16">
+      <c r="G1184" s="14">
         <v>84</v>
       </c>
-      <c r="H1184" s="15">
+      <c r="H1184" s="13">
         <v>-135</v>
       </c>
-      <c r="I1184" s="16">
+      <c r="I1184" s="14">
         <v>102</v>
       </c>
-      <c r="J1184" s="15">
+      <c r="J1184" s="13">
         <v>-30</v>
       </c>
       <c r="K1184"/>
       <c r="L1184"/>
-      <c r="M1184" s="15">
+      <c r="M1184" s="13">
         <v>1</v>
       </c>
       <c r="N1184" s="11">
@@ -51208,35 +51223,35 @@
       <c r="A1185" s="1">
         <v>80</v>
       </c>
-      <c r="B1185" s="15">
+      <c r="B1185" s="13">
         <v>12</v>
       </c>
-      <c r="C1185" s="16" t="s">
+      <c r="C1185" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="D1185" s="15">
+      <c r="D1185" s="13">
         <v>55</v>
       </c>
-      <c r="E1185" s="15">
+      <c r="E1185" s="13">
         <v>13.5</v>
       </c>
-      <c r="F1185" s="15">
+      <c r="F1185" s="13">
         <v>22</v>
       </c>
-      <c r="G1185" s="16">
+      <c r="G1185" s="14">
         <v>96</v>
       </c>
-      <c r="H1185" s="15">
+      <c r="H1185" s="13">
         <v>24</v>
       </c>
-      <c r="I1185" s="16">
+      <c r="I1185" s="14">
         <v>97</v>
       </c>
-      <c r="J1185" s="15">
+      <c r="J1185" s="13">
         <v>35</v>
       </c>
       <c r="K1185"/>
-      <c r="L1185" s="15">
+      <c r="L1185" s="13">
         <v>1</v>
       </c>
       <c r="M1185"/>
@@ -51251,35 +51266,35 @@
       <c r="A1186" s="1">
         <v>80</v>
       </c>
-      <c r="B1186" s="15">
+      <c r="B1186" s="13">
         <v>13</v>
       </c>
-      <c r="C1186" s="16" t="s">
+      <c r="C1186" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D1186" s="15">
+      <c r="D1186" s="13">
         <v>58</v>
       </c>
-      <c r="E1186" s="15">
+      <c r="E1186" s="13">
         <v>29.3</v>
       </c>
-      <c r="F1186" s="15">
+      <c r="F1186" s="13">
         <v>21</v>
       </c>
-      <c r="G1186" s="16">
+      <c r="G1186" s="14">
         <v>87</v>
       </c>
-      <c r="H1186" s="15">
+      <c r="H1186" s="13">
         <v>-72</v>
       </c>
-      <c r="I1186" s="16">
+      <c r="I1186" s="14">
         <v>110</v>
       </c>
-      <c r="J1186" s="15">
+      <c r="J1186" s="13">
         <v>32</v>
       </c>
       <c r="K1186"/>
-      <c r="L1186" s="15">
+      <c r="L1186" s="13">
         <v>1</v>
       </c>
       <c r="M1186"/>
@@ -51294,34 +51309,34 @@
       <c r="A1187" s="1">
         <v>81</v>
       </c>
-      <c r="B1187" s="15">
-        <v>1</v>
-      </c>
-      <c r="C1187" s="16" t="s">
+      <c r="B1187" s="13">
+        <v>1</v>
+      </c>
+      <c r="C1187" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D1187" s="15">
+      <c r="D1187" s="13">
         <v>57</v>
       </c>
-      <c r="E1187" s="15">
+      <c r="E1187" s="13">
         <v>84.9</v>
       </c>
-      <c r="F1187" s="15">
+      <c r="F1187" s="13">
         <v>62</v>
       </c>
-      <c r="G1187" s="16">
+      <c r="G1187" s="14">
         <v>107</v>
       </c>
-      <c r="H1187" s="15">
+      <c r="H1187" s="13">
         <v>67</v>
       </c>
-      <c r="I1187" s="16">
+      <c r="I1187" s="14">
         <v>111</v>
       </c>
-      <c r="J1187" s="15">
+      <c r="J1187" s="13">
         <v>54</v>
       </c>
-      <c r="K1187" s="15">
+      <c r="K1187" s="13">
         <v>1</v>
       </c>
       <c r="L1187"/>
@@ -51337,36 +51352,36 @@
       <c r="A1188" s="1">
         <v>81</v>
       </c>
-      <c r="B1188" s="15">
+      <c r="B1188" s="13">
         <v>2</v>
       </c>
-      <c r="C1188" s="16" t="s">
+      <c r="C1188" s="14" t="s">
         <v>718</v>
       </c>
-      <c r="D1188" s="15">
+      <c r="D1188" s="13">
         <v>57</v>
       </c>
-      <c r="E1188" s="15">
+      <c r="E1188" s="13">
         <v>28.9</v>
       </c>
-      <c r="F1188" s="15">
+      <c r="F1188" s="13">
         <v>26</v>
       </c>
-      <c r="G1188" s="16">
+      <c r="G1188" s="14">
         <v>101</v>
       </c>
-      <c r="H1188" s="15">
+      <c r="H1188" s="13">
         <v>86</v>
       </c>
-      <c r="I1188" s="16">
+      <c r="I1188" s="14">
         <v>77</v>
       </c>
-      <c r="J1188" s="15">
+      <c r="J1188" s="13">
         <v>47</v>
       </c>
       <c r="K1188"/>
       <c r="L1188"/>
-      <c r="M1188" s="15">
+      <c r="M1188" s="13">
         <v>1</v>
       </c>
       <c r="N1188" s="11">
@@ -51380,36 +51395,36 @@
       <c r="A1189" s="1">
         <v>81</v>
       </c>
-      <c r="B1189" s="15">
+      <c r="B1189" s="13">
         <v>3</v>
       </c>
-      <c r="C1189" s="16" t="s">
+      <c r="C1189" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="D1189" s="15">
+      <c r="D1189" s="13">
         <v>57</v>
       </c>
-      <c r="E1189" s="15">
+      <c r="E1189" s="13">
         <v>19.5</v>
       </c>
-      <c r="F1189" s="15">
+      <c r="F1189" s="13">
         <v>32</v>
       </c>
-      <c r="G1189" s="16">
+      <c r="G1189" s="14">
         <v>103</v>
       </c>
-      <c r="H1189" s="15">
+      <c r="H1189" s="13">
         <v>73</v>
       </c>
-      <c r="I1189" s="16">
+      <c r="I1189" s="14">
         <v>87</v>
       </c>
-      <c r="J1189" s="15">
+      <c r="J1189" s="13">
         <v>18</v>
       </c>
       <c r="K1189"/>
       <c r="L1189"/>
-      <c r="M1189" s="15">
+      <c r="M1189" s="13">
         <v>1</v>
       </c>
       <c r="N1189" s="11">
@@ -51423,37 +51438,37 @@
       <c r="A1190" s="1">
         <v>81</v>
       </c>
-      <c r="B1190" s="15">
+      <c r="B1190" s="13">
         <v>4</v>
       </c>
-      <c r="C1190" s="16" t="s">
+      <c r="C1190" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="D1190" s="15">
+      <c r="D1190" s="13">
         <v>57</v>
       </c>
-      <c r="E1190" s="15">
+      <c r="E1190" s="13">
         <v>21.1</v>
       </c>
-      <c r="F1190" s="15">
+      <c r="F1190" s="13">
         <v>28</v>
       </c>
-      <c r="G1190" s="16">
+      <c r="G1190" s="14">
         <v>104</v>
       </c>
-      <c r="H1190" s="15">
+      <c r="H1190" s="13">
         <v>51</v>
       </c>
-      <c r="I1190" s="16">
+      <c r="I1190" s="14">
         <v>92</v>
       </c>
-      <c r="J1190" s="15">
+      <c r="J1190" s="13">
         <v>-129</v>
       </c>
-      <c r="K1190" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1190" s="15">
+      <c r="K1190" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1190" s="13">
         <v>1</v>
       </c>
       <c r="M1190"/>
@@ -51468,31 +51483,31 @@
       <c r="A1191" s="1">
         <v>81</v>
       </c>
-      <c r="B1191" s="15">
+      <c r="B1191" s="13">
         <v>5</v>
       </c>
-      <c r="C1191" s="16" t="s">
+      <c r="C1191" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="D1191" s="15">
+      <c r="D1191" s="13">
         <v>57</v>
       </c>
-      <c r="E1191" s="15">
+      <c r="E1191" s="13">
         <v>19.3</v>
       </c>
-      <c r="F1191" s="15">
+      <c r="F1191" s="13">
         <v>26</v>
       </c>
-      <c r="G1191" s="16">
+      <c r="G1191" s="14">
         <v>97</v>
       </c>
-      <c r="H1191" s="15">
+      <c r="H1191" s="13">
         <v>39</v>
       </c>
-      <c r="I1191" s="16">
+      <c r="I1191" s="14">
         <v>85</v>
       </c>
-      <c r="J1191" s="15">
+      <c r="J1191" s="13">
         <v>25</v>
       </c>
       <c r="K1191"/>
@@ -51509,40 +51524,40 @@
       <c r="A1192" s="1">
         <v>81</v>
       </c>
-      <c r="B1192" s="15">
+      <c r="B1192" s="13">
         <v>6</v>
       </c>
-      <c r="C1192" s="16" t="s">
+      <c r="C1192" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D1192" s="15">
+      <c r="D1192" s="13">
         <v>57</v>
       </c>
-      <c r="E1192" s="15">
+      <c r="E1192" s="13">
         <v>12</v>
       </c>
-      <c r="F1192" s="15">
+      <c r="F1192" s="13">
         <v>14</v>
       </c>
-      <c r="G1192" s="16">
+      <c r="G1192" s="14">
         <v>100</v>
       </c>
-      <c r="H1192" s="15">
+      <c r="H1192" s="13">
         <v>-46</v>
       </c>
-      <c r="I1192" s="16">
+      <c r="I1192" s="14">
         <v>108</v>
       </c>
-      <c r="J1192" s="15">
+      <c r="J1192" s="13">
         <v>7</v>
       </c>
-      <c r="K1192" s="15">
-        <v>1</v>
-      </c>
-      <c r="L1192" s="15">
-        <v>1</v>
-      </c>
-      <c r="M1192" s="15">
+      <c r="K1192" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1192" s="13">
+        <v>1</v>
+      </c>
+      <c r="M1192" s="13">
         <v>1</v>
       </c>
       <c r="N1192" s="11">
@@ -51556,35 +51571,35 @@
       <c r="A1193" s="1">
         <v>81</v>
       </c>
-      <c r="B1193" s="15">
+      <c r="B1193" s="13">
         <v>7</v>
       </c>
-      <c r="C1193" s="16" t="s">
+      <c r="C1193" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="D1193" s="15">
+      <c r="D1193" s="13">
         <v>57</v>
       </c>
-      <c r="E1193" s="15">
+      <c r="E1193" s="13">
         <v>40.3</v>
       </c>
-      <c r="F1193" s="15">
+      <c r="F1193" s="13">
         <v>29</v>
       </c>
-      <c r="G1193" s="16">
+      <c r="G1193" s="14">
         <v>104</v>
       </c>
-      <c r="H1193" s="15">
+      <c r="H1193" s="13">
         <v>27</v>
       </c>
-      <c r="I1193" s="16">
+      <c r="I1193" s="14">
         <v>113</v>
       </c>
-      <c r="J1193" s="15">
+      <c r="J1193" s="13">
         <v>81</v>
       </c>
       <c r="K1193"/>
-      <c r="L1193" s="15">
+      <c r="L1193" s="13">
         <v>1</v>
       </c>
       <c r="M1193"/>
@@ -51599,31 +51614,31 @@
       <c r="A1194" s="1">
         <v>81</v>
       </c>
-      <c r="B1194" s="15">
+      <c r="B1194" s="13">
         <v>8</v>
       </c>
-      <c r="C1194" s="16" t="s">
+      <c r="C1194" s="14" t="s">
         <v>719</v>
       </c>
-      <c r="D1194" s="15">
+      <c r="D1194" s="13">
         <v>57</v>
       </c>
-      <c r="E1194" s="15">
+      <c r="E1194" s="13">
         <v>7.3</v>
       </c>
-      <c r="F1194" s="15">
+      <c r="F1194" s="13">
         <v>8</v>
       </c>
-      <c r="G1194" s="16">
+      <c r="G1194" s="14">
         <v>92</v>
       </c>
-      <c r="H1194" s="15">
+      <c r="H1194" s="13">
         <v>24</v>
       </c>
-      <c r="I1194" s="16">
+      <c r="I1194" s="14">
         <v>93</v>
       </c>
-      <c r="J1194" s="15">
+      <c r="J1194" s="13">
         <v>37</v>
       </c>
       <c r="K1194"/>
@@ -51640,35 +51655,35 @@
       <c r="A1195" s="1">
         <v>81</v>
       </c>
-      <c r="B1195" s="15">
+      <c r="B1195" s="13">
         <v>9</v>
       </c>
-      <c r="C1195" s="16" t="s">
+      <c r="C1195" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="D1195" s="15">
+      <c r="D1195" s="13">
         <v>57</v>
       </c>
-      <c r="E1195" s="15">
+      <c r="E1195" s="13">
         <v>38.3</v>
       </c>
-      <c r="F1195" s="15">
+      <c r="F1195" s="13">
         <v>24</v>
       </c>
-      <c r="G1195" s="16">
+      <c r="G1195" s="14">
         <v>97</v>
       </c>
-      <c r="H1195" s="15">
+      <c r="H1195" s="13">
         <v>-73</v>
       </c>
-      <c r="I1195" s="16">
+      <c r="I1195" s="14">
         <v>107</v>
       </c>
-      <c r="J1195" s="15">
+      <c r="J1195" s="13">
         <v>34</v>
       </c>
       <c r="K1195"/>
-      <c r="L1195" s="15">
+      <c r="L1195" s="13">
         <v>1</v>
       </c>
       <c r="M1195"/>
@@ -51683,36 +51698,36 @@
       <c r="A1196" s="1">
         <v>81</v>
       </c>
-      <c r="B1196" s="15">
+      <c r="B1196" s="13">
         <v>10</v>
       </c>
-      <c r="C1196" s="16" t="s">
+      <c r="C1196" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="D1196" s="15">
+      <c r="D1196" s="13">
         <v>57</v>
       </c>
-      <c r="E1196" s="15">
+      <c r="E1196" s="13">
         <v>21.1</v>
       </c>
-      <c r="F1196" s="15">
+      <c r="F1196" s="13">
         <v>25</v>
       </c>
-      <c r="G1196" s="16">
+      <c r="G1196" s="14">
         <v>94</v>
       </c>
-      <c r="H1196" s="15">
+      <c r="H1196" s="13">
         <v>58</v>
       </c>
-      <c r="I1196" s="16">
+      <c r="I1196" s="14">
         <v>97</v>
       </c>
-      <c r="J1196" s="15">
+      <c r="J1196" s="13">
         <v>41</v>
       </c>
       <c r="K1196"/>
       <c r="L1196"/>
-      <c r="M1196" s="15">
+      <c r="M1196" s="13">
         <v>1</v>
       </c>
       <c r="N1196" s="11">
@@ -51726,31 +51741,31 @@
       <c r="A1197" s="1">
         <v>81</v>
       </c>
-      <c r="B1197" s="15">
+      <c r="B1197" s="13">
         <v>11</v>
       </c>
-      <c r="C1197" s="16" t="s">
+      <c r="C1197" s="14" t="s">
         <v>720</v>
       </c>
-      <c r="D1197" s="15">
+      <c r="D1197" s="13">
         <v>57</v>
       </c>
-      <c r="E1197" s="15">
+      <c r="E1197" s="13">
         <v>7.4</v>
       </c>
-      <c r="F1197" s="15">
+      <c r="F1197" s="13">
         <v>16</v>
       </c>
-      <c r="G1197" s="16">
+      <c r="G1197" s="14">
         <v>69</v>
       </c>
-      <c r="H1197" s="15">
+      <c r="H1197" s="13">
         <v>94</v>
       </c>
-      <c r="I1197" s="16">
+      <c r="I1197" s="14">
         <v>68</v>
       </c>
-      <c r="J1197" s="15">
+      <c r="J1197" s="13">
         <v>34</v>
       </c>
       <c r="K1197"/>
@@ -51760,6 +51775,674 @@
         <v>0</v>
       </c>
       <c r="O1197" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:15">
+      <c r="A1198" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1198" s="13">
+        <v>1</v>
+      </c>
+      <c r="C1198" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1198" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1198" s="13">
+        <v>13.4</v>
+      </c>
+      <c r="F1198" s="13">
+        <v>16</v>
+      </c>
+      <c r="G1198" s="14">
+        <v>92</v>
+      </c>
+      <c r="H1198" s="13">
+        <v>-59</v>
+      </c>
+      <c r="I1198" s="14">
+        <v>93</v>
+      </c>
+      <c r="J1198" s="13">
+        <v>-132</v>
+      </c>
+      <c r="K1198" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1198"/>
+      <c r="M1198" s="13">
+        <v>1</v>
+      </c>
+      <c r="N1198" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1198" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:15">
+      <c r="A1199" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1199" s="13">
+        <v>2</v>
+      </c>
+      <c r="C1199" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1199" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1199" s="13">
+        <v>17.5</v>
+      </c>
+      <c r="F1199" s="13">
+        <v>17</v>
+      </c>
+      <c r="G1199" s="14">
+        <v>89</v>
+      </c>
+      <c r="H1199" s="13">
+        <v>51</v>
+      </c>
+      <c r="I1199" s="14">
+        <v>93</v>
+      </c>
+      <c r="J1199" s="13">
+        <v>-44</v>
+      </c>
+      <c r="K1199"/>
+      <c r="L1199">
+        <v>1</v>
+      </c>
+      <c r="M1199"/>
+      <c r="N1199" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1199" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:15">
+      <c r="A1200" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1200" s="13">
+        <v>3</v>
+      </c>
+      <c r="C1200" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1200" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1200" s="13">
+        <v>13.8</v>
+      </c>
+      <c r="F1200" s="13">
+        <v>19</v>
+      </c>
+      <c r="G1200" s="14">
+        <v>93</v>
+      </c>
+      <c r="H1200" s="13">
+        <v>35</v>
+      </c>
+      <c r="I1200" s="14">
+        <v>85</v>
+      </c>
+      <c r="J1200" s="13">
+        <v>-24</v>
+      </c>
+      <c r="K1200"/>
+      <c r="L1200"/>
+      <c r="M1200" s="13">
+        <v>1</v>
+      </c>
+      <c r="N1200" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1200" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:15">
+      <c r="A1201" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1201" s="13">
+        <v>4</v>
+      </c>
+      <c r="C1201" s="14" t="s">
+        <v>721</v>
+      </c>
+      <c r="D1201" s="13">
+        <v>55</v>
+      </c>
+      <c r="E1201" s="13">
+        <v>4.3</v>
+      </c>
+      <c r="F1201" s="13">
+        <v>1</v>
+      </c>
+      <c r="G1201" s="14">
+        <v>90</v>
+      </c>
+      <c r="H1201" s="13">
+        <v>-77</v>
+      </c>
+      <c r="I1201" s="14">
+        <v>95</v>
+      </c>
+      <c r="J1201" s="13">
+        <v>-76</v>
+      </c>
+      <c r="K1201"/>
+      <c r="L1201"/>
+      <c r="M1201"/>
+      <c r="N1201" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1201" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:15">
+      <c r="A1202" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1202" s="13">
+        <v>5</v>
+      </c>
+      <c r="C1202" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1202" s="13">
+        <v>57.5</v>
+      </c>
+      <c r="E1202" s="13">
+        <v>12.7</v>
+      </c>
+      <c r="F1202" s="13">
+        <v>16</v>
+      </c>
+      <c r="G1202" s="14">
+        <v>92</v>
+      </c>
+      <c r="H1202" s="13">
+        <v>37</v>
+      </c>
+      <c r="I1202" s="14">
+        <v>95</v>
+      </c>
+      <c r="J1202" s="13">
+        <v>77</v>
+      </c>
+      <c r="K1202"/>
+      <c r="L1202"/>
+      <c r="M1202"/>
+      <c r="N1202" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1202" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:15">
+      <c r="A1203" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1203" s="13">
+        <v>6</v>
+      </c>
+      <c r="C1203" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1203" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1203" s="13">
+        <v>19.9</v>
+      </c>
+      <c r="F1203" s="13">
+        <v>24</v>
+      </c>
+      <c r="G1203" s="14">
+        <v>102</v>
+      </c>
+      <c r="H1203" s="13">
+        <v>-3</v>
+      </c>
+      <c r="I1203" s="14">
+        <v>97</v>
+      </c>
+      <c r="J1203" s="13">
+        <v>58</v>
+      </c>
+      <c r="K1203" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1203">
+        <v>1</v>
+      </c>
+      <c r="M1203" s="13">
+        <v>1</v>
+      </c>
+      <c r="N1203" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1203" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:15">
+      <c r="A1204" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1204" s="13">
+        <v>7</v>
+      </c>
+      <c r="C1204" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="D1204" s="13">
+        <v>55</v>
+      </c>
+      <c r="E1204" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="F1204" s="13">
+        <v>8</v>
+      </c>
+      <c r="G1204" s="14">
+        <v>90</v>
+      </c>
+      <c r="H1204" s="13">
+        <v>3</v>
+      </c>
+      <c r="I1204" s="14">
+        <v>86</v>
+      </c>
+      <c r="J1204" s="13">
+        <v>-160</v>
+      </c>
+      <c r="K1204"/>
+      <c r="L1204"/>
+      <c r="M1204"/>
+      <c r="N1204" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1204" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:15">
+      <c r="A1205" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1205" s="13">
+        <v>8</v>
+      </c>
+      <c r="C1205" s="14" t="s">
+        <v>724</v>
+      </c>
+      <c r="D1205" s="13">
+        <v>55</v>
+      </c>
+      <c r="E1205" s="13">
+        <v>15.5</v>
+      </c>
+      <c r="F1205" s="13">
+        <v>16</v>
+      </c>
+      <c r="G1205" s="14">
+        <v>101</v>
+      </c>
+      <c r="H1205" s="13">
+        <v>75</v>
+      </c>
+      <c r="I1205" s="14">
+        <v>87</v>
+      </c>
+      <c r="J1205" s="13">
+        <v>36</v>
+      </c>
+      <c r="K1205" s="13">
+        <v>1</v>
+      </c>
+      <c r="L1205"/>
+      <c r="M1205"/>
+      <c r="N1205" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1205" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:15">
+      <c r="A1206" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1206" s="13">
+        <v>9</v>
+      </c>
+      <c r="C1206" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1206" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1206" s="13">
+        <v>4.9</v>
+      </c>
+      <c r="F1206" s="13">
+        <v>8</v>
+      </c>
+      <c r="G1206" s="14">
+        <v>86</v>
+      </c>
+      <c r="H1206" s="13">
+        <v>-210</v>
+      </c>
+      <c r="I1206" s="14">
+        <v>83</v>
+      </c>
+      <c r="J1206" s="13">
+        <v>-97</v>
+      </c>
+      <c r="K1206"/>
+      <c r="L1206"/>
+      <c r="M1206" s="13">
+        <v>1</v>
+      </c>
+      <c r="N1206" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1206" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:15">
+      <c r="A1207" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1207" s="13">
+        <v>10</v>
+      </c>
+      <c r="C1207" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1207" s="13">
+        <v>56</v>
+      </c>
+      <c r="E1207" s="13">
+        <v>28.4</v>
+      </c>
+      <c r="F1207" s="13">
+        <v>22</v>
+      </c>
+      <c r="G1207" s="14">
+        <v>88</v>
+      </c>
+      <c r="H1207" s="13">
+        <v>-5</v>
+      </c>
+      <c r="I1207" s="14">
+        <v>95</v>
+      </c>
+      <c r="J1207" s="13">
+        <v>-20</v>
+      </c>
+      <c r="K1207"/>
+      <c r="L1207">
+        <v>1</v>
+      </c>
+      <c r="M1207"/>
+      <c r="N1207" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1207" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:15">
+      <c r="A1208" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1208" s="13">
+        <v>11</v>
+      </c>
+      <c r="C1208" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1208" s="13">
+        <v>58.5</v>
+      </c>
+      <c r="E1208" s="13">
+        <v>40</v>
+      </c>
+      <c r="F1208" s="13">
+        <v>28</v>
+      </c>
+      <c r="G1208" s="14">
+        <v>95</v>
+      </c>
+      <c r="H1208" s="13">
+        <v>-40</v>
+      </c>
+      <c r="I1208" s="14">
+        <v>102</v>
+      </c>
+      <c r="J1208" s="13">
+        <v>59</v>
+      </c>
+      <c r="K1208"/>
+      <c r="L1208"/>
+      <c r="M1208"/>
+      <c r="N1208" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1208" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:15">
+      <c r="A1209" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1209" s="13">
+        <v>12</v>
+      </c>
+      <c r="C1209" s="14" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1209" s="13">
+        <v>55</v>
+      </c>
+      <c r="E1209" s="13">
+        <v>10.8</v>
+      </c>
+      <c r="F1209" s="13">
+        <v>15</v>
+      </c>
+      <c r="G1209" s="14">
+        <v>104</v>
+      </c>
+      <c r="H1209" s="13">
+        <v>70</v>
+      </c>
+      <c r="I1209" s="14">
+        <v>100</v>
+      </c>
+      <c r="J1209" s="13">
+        <v>65</v>
+      </c>
+      <c r="K1209"/>
+      <c r="L1209"/>
+      <c r="M1209"/>
+      <c r="N1209" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1209" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:15">
+      <c r="A1210" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1210" s="13">
+        <v>13</v>
+      </c>
+      <c r="C1210" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1210" s="13">
+        <v>59</v>
+      </c>
+      <c r="E1210" s="13">
+        <v>53.7</v>
+      </c>
+      <c r="F1210" s="13">
+        <v>44</v>
+      </c>
+      <c r="G1210" s="14">
+        <v>119</v>
+      </c>
+      <c r="H1210" s="13">
+        <v>-3</v>
+      </c>
+      <c r="I1210" s="14">
+        <v>105</v>
+      </c>
+      <c r="J1210" s="13">
+        <v>-4</v>
+      </c>
+      <c r="K1210"/>
+      <c r="L1210"/>
+      <c r="M1210"/>
+      <c r="N1210" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1210" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:15">
+      <c r="A1211" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1211" s="13">
+        <v>14</v>
+      </c>
+      <c r="C1211" s="14" t="s">
+        <v>726</v>
+      </c>
+      <c r="D1211" s="13">
+        <v>57</v>
+      </c>
+      <c r="E1211" s="13">
+        <v>31.9</v>
+      </c>
+      <c r="F1211" s="13">
+        <v>23</v>
+      </c>
+      <c r="G1211" s="14">
+        <v>106</v>
+      </c>
+      <c r="H1211" s="13">
+        <v>66</v>
+      </c>
+      <c r="I1211" s="14">
+        <v>98</v>
+      </c>
+      <c r="J1211" s="13">
+        <v>18</v>
+      </c>
+      <c r="K1211"/>
+      <c r="L1211"/>
+      <c r="M1211"/>
+      <c r="N1211" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1211" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:15">
+      <c r="A1212" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1212" s="13">
+        <v>15</v>
+      </c>
+      <c r="C1212" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="D1212" s="13">
+        <v>58</v>
+      </c>
+      <c r="E1212" s="13">
+        <v>24.7</v>
+      </c>
+      <c r="F1212" s="13">
+        <v>28</v>
+      </c>
+      <c r="G1212" s="14">
+        <v>90</v>
+      </c>
+      <c r="H1212" s="13">
+        <v>42</v>
+      </c>
+      <c r="I1212" s="14">
+        <v>115</v>
+      </c>
+      <c r="J1212" s="13">
+        <v>-63</v>
+      </c>
+      <c r="K1212"/>
+      <c r="L1212"/>
+      <c r="M1212"/>
+      <c r="N1212" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1212" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:15">
+      <c r="A1213" s="1">
+        <v>82</v>
+      </c>
+      <c r="B1213" s="13">
+        <v>16</v>
+      </c>
+      <c r="C1213" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1213" s="13">
+        <v>54</v>
+      </c>
+      <c r="E1213" s="13">
+        <v>3.2</v>
+      </c>
+      <c r="F1213" s="13">
+        <v>1</v>
+      </c>
+      <c r="G1213"/>
+      <c r="H1213"/>
+      <c r="I1213"/>
+      <c r="J1213"/>
+      <c r="K1213"/>
+      <c r="L1213"/>
+      <c r="M1213"/>
+      <c r="N1213" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1213" s="11">
         <v>0</v>
       </c>
     </row>
@@ -51849,7 +52532,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{80d01843-df05-4d80-a2cc-2857e5e5fb9a}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{b5cce397-cf48-46de-9f4c-f443b9a90bb4}">
             <xm:f>NOT(ISERROR(SEARCH(#REF!,M61)))</xm:f>
             <xm:f>#REF!</xm:f>
             <x14:dxf>

--- a/train_data3.xlsx
+++ b/train_data3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="728">
   <si>
     <t>レースID</t>
   </si>
@@ -2887,7 +2887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2924,6 +2924,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -3320,7 +3326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1213"/>
+  <dimension ref="A1:O1231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" width="8.72222222222222" style="1"/>
@@ -52445,6 +52451,726 @@
       <c r="O1213" s="11">
         <v>0</v>
       </c>
+    </row>
+    <row r="1214" spans="1:15">
+      <c r="A1214" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1214" s="15">
+        <v>1</v>
+      </c>
+      <c r="C1214" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1214" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1214" s="15">
+        <v>4.6</v>
+      </c>
+      <c r="F1214" s="15">
+        <v>6</v>
+      </c>
+      <c r="G1214" s="16">
+        <v>74</v>
+      </c>
+      <c r="H1214" s="15">
+        <v>-119</v>
+      </c>
+      <c r="I1214" s="16">
+        <v>115</v>
+      </c>
+      <c r="J1214" s="15">
+        <v>16</v>
+      </c>
+      <c r="K1214"/>
+      <c r="L1214"/>
+      <c r="M1214"/>
+      <c r="N1214" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1214" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:15">
+      <c r="A1215" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1215" s="15">
+        <v>2</v>
+      </c>
+      <c r="C1215" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1215" s="15">
+        <v>56</v>
+      </c>
+      <c r="E1215" s="15">
+        <v>9.3</v>
+      </c>
+      <c r="F1215" s="15">
+        <v>13</v>
+      </c>
+      <c r="G1215" s="16">
+        <v>106</v>
+      </c>
+      <c r="H1215" s="15">
+        <v>9</v>
+      </c>
+      <c r="I1215" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1215" s="15">
+        <v>35</v>
+      </c>
+      <c r="K1215" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1215"/>
+      <c r="M1215"/>
+      <c r="N1215" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1215" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:15">
+      <c r="A1216" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1216" s="15">
+        <v>3</v>
+      </c>
+      <c r="C1216" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1216" s="15">
+        <v>56</v>
+      </c>
+      <c r="E1216" s="15">
+        <v>10.6</v>
+      </c>
+      <c r="F1216" s="15">
+        <v>18</v>
+      </c>
+      <c r="G1216" s="16">
+        <v>106</v>
+      </c>
+      <c r="H1216" s="15">
+        <v>50</v>
+      </c>
+      <c r="I1216" s="16">
+        <v>106</v>
+      </c>
+      <c r="J1216" s="15">
+        <v>50</v>
+      </c>
+      <c r="K1216"/>
+      <c r="L1216" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1216"/>
+      <c r="N1216" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1216" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:15">
+      <c r="A1217" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1217" s="15">
+        <v>4</v>
+      </c>
+      <c r="C1217" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1217" s="15">
+        <v>56</v>
+      </c>
+      <c r="E1217" s="15">
+        <v>6.2</v>
+      </c>
+      <c r="F1217" s="15">
+        <v>6</v>
+      </c>
+      <c r="G1217" s="16">
+        <v>86</v>
+      </c>
+      <c r="H1217" s="15">
+        <v>-113</v>
+      </c>
+      <c r="I1217" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1217" s="15">
+        <v>-25</v>
+      </c>
+      <c r="K1217" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1217" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1217" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1217" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1217" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:15">
+      <c r="A1218" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1218" s="15">
+        <v>5</v>
+      </c>
+      <c r="C1218" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="D1218" s="15">
+        <v>56</v>
+      </c>
+      <c r="E1218" s="15">
+        <v>9.1</v>
+      </c>
+      <c r="F1218" s="15">
+        <v>18</v>
+      </c>
+      <c r="G1218" s="16">
+        <v>109</v>
+      </c>
+      <c r="H1218" s="15">
+        <v>58</v>
+      </c>
+      <c r="I1218" s="16">
+        <v>89</v>
+      </c>
+      <c r="J1218" s="15">
+        <v>-34</v>
+      </c>
+      <c r="K1218" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1218"/>
+      <c r="M1218" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1218" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1218" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:15">
+      <c r="A1219" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1219" s="15">
+        <v>6</v>
+      </c>
+      <c r="C1219" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D1219" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1219" s="15">
+        <v>27.3</v>
+      </c>
+      <c r="F1219" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1219" s="16">
+        <v>103</v>
+      </c>
+      <c r="H1219" s="15">
+        <v>14</v>
+      </c>
+      <c r="I1219" s="16">
+        <v>111</v>
+      </c>
+      <c r="J1219" s="15">
+        <v>61</v>
+      </c>
+      <c r="K1219"/>
+      <c r="L1219" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1219" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1219" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1219" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:15">
+      <c r="A1220" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1220" s="15">
+        <v>7</v>
+      </c>
+      <c r="C1220" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1220" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1220" s="15">
+        <v>6</v>
+      </c>
+      <c r="F1220" s="15">
+        <v>9</v>
+      </c>
+      <c r="G1220" s="16">
+        <v>105</v>
+      </c>
+      <c r="H1220" s="15">
+        <v>-44</v>
+      </c>
+      <c r="I1220" s="16">
+        <v>103</v>
+      </c>
+      <c r="J1220" s="15">
+        <v>26</v>
+      </c>
+      <c r="K1220"/>
+      <c r="L1220"/>
+      <c r="M1220"/>
+      <c r="N1220" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1220" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:15">
+      <c r="A1221" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1221" s="15">
+        <v>8</v>
+      </c>
+      <c r="C1221" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1221" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1221" s="15">
+        <v>15.6</v>
+      </c>
+      <c r="F1221" s="15">
+        <v>12</v>
+      </c>
+      <c r="G1221" s="16">
+        <v>105</v>
+      </c>
+      <c r="H1221" s="15">
+        <v>44</v>
+      </c>
+      <c r="I1221" s="16">
+        <v>101</v>
+      </c>
+      <c r="J1221" s="15">
+        <v>24</v>
+      </c>
+      <c r="K1221"/>
+      <c r="L1221"/>
+      <c r="M1221"/>
+      <c r="N1221" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1221" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:15">
+      <c r="A1222" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1222" s="15">
+        <v>9</v>
+      </c>
+      <c r="C1222" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1222" s="15">
+        <v>54</v>
+      </c>
+      <c r="E1222" s="15">
+        <v>49.1</v>
+      </c>
+      <c r="F1222" s="15">
+        <v>33</v>
+      </c>
+      <c r="G1222" s="16">
+        <v>83</v>
+      </c>
+      <c r="H1222" s="15">
+        <v>-24</v>
+      </c>
+      <c r="I1222" s="16">
+        <v>112</v>
+      </c>
+      <c r="J1222" s="15">
+        <v>90</v>
+      </c>
+      <c r="K1222"/>
+      <c r="L1222"/>
+      <c r="M1222"/>
+      <c r="N1222" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1222" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:15">
+      <c r="A1223" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1223" s="15">
+        <v>10</v>
+      </c>
+      <c r="C1223" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1223" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1223" s="15">
+        <v>14.5</v>
+      </c>
+      <c r="F1223" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1223" s="16">
+        <v>104</v>
+      </c>
+      <c r="H1223" s="15">
+        <v>29</v>
+      </c>
+      <c r="I1223" s="16">
+        <v>100</v>
+      </c>
+      <c r="J1223" s="15">
+        <v>10</v>
+      </c>
+      <c r="K1223"/>
+      <c r="L1223"/>
+      <c r="M1223"/>
+      <c r="N1223" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1223" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:15">
+      <c r="A1224" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1224" s="15">
+        <v>11</v>
+      </c>
+      <c r="C1224" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1224" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1224" s="15">
+        <v>20.3</v>
+      </c>
+      <c r="F1224" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1224" s="16">
+        <v>102</v>
+      </c>
+      <c r="H1224" s="15">
+        <v>58</v>
+      </c>
+      <c r="I1224" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1224" s="15">
+        <v>58</v>
+      </c>
+      <c r="K1224"/>
+      <c r="L1224"/>
+      <c r="M1224" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1224" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1224" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:15">
+      <c r="A1225" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1225" s="15">
+        <v>12</v>
+      </c>
+      <c r="C1225" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1225" s="15">
+        <v>54</v>
+      </c>
+      <c r="E1225" s="15">
+        <v>7.2</v>
+      </c>
+      <c r="F1225" s="15">
+        <v>18</v>
+      </c>
+      <c r="G1225" s="16">
+        <v>88</v>
+      </c>
+      <c r="H1225" s="15">
+        <v>20</v>
+      </c>
+      <c r="I1225" s="16">
+        <v>91</v>
+      </c>
+      <c r="J1225" s="15">
+        <v>25</v>
+      </c>
+      <c r="K1225"/>
+      <c r="L1225"/>
+      <c r="M1225" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1225" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1225" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:15">
+      <c r="A1226" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1226" s="15">
+        <v>13</v>
+      </c>
+      <c r="C1226" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1226" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1226" s="15">
+        <v>54.5</v>
+      </c>
+      <c r="F1226" s="15">
+        <v>34</v>
+      </c>
+      <c r="G1226" s="16">
+        <v>106</v>
+      </c>
+      <c r="H1226" s="15">
+        <v>54</v>
+      </c>
+      <c r="I1226" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1226" s="15">
+        <v>38</v>
+      </c>
+      <c r="K1226"/>
+      <c r="L1226" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1226"/>
+      <c r="N1226" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1226" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:15">
+      <c r="A1227" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1227" s="15">
+        <v>14</v>
+      </c>
+      <c r="C1227" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1227" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1227" s="15">
+        <v>15.8</v>
+      </c>
+      <c r="F1227" s="15">
+        <v>16</v>
+      </c>
+      <c r="G1227" s="16">
+        <v>105</v>
+      </c>
+      <c r="H1227" s="15">
+        <v>24</v>
+      </c>
+      <c r="I1227" s="16">
+        <v>115</v>
+      </c>
+      <c r="J1227" s="15">
+        <v>67</v>
+      </c>
+      <c r="K1227"/>
+      <c r="L1227"/>
+      <c r="M1227" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1227" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1227" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:15">
+      <c r="A1228" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1228" s="15">
+        <v>15</v>
+      </c>
+      <c r="C1228" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1228" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1228" s="15">
+        <v>33.7</v>
+      </c>
+      <c r="F1228" s="15">
+        <v>30</v>
+      </c>
+      <c r="G1228" s="16">
+        <v>111</v>
+      </c>
+      <c r="H1228" s="15">
+        <v>55</v>
+      </c>
+      <c r="I1228" s="16">
+        <v>97</v>
+      </c>
+      <c r="J1228" s="15">
+        <v>19</v>
+      </c>
+      <c r="K1228"/>
+      <c r="L1228"/>
+      <c r="M1228" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1228" s="11">
+        <v>0</v>
+      </c>
+      <c r="O1228" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:15">
+      <c r="A1229" s="15">
+        <v>83</v>
+      </c>
+      <c r="B1229" s="15">
+        <v>16</v>
+      </c>
+      <c r="C1229" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1229" s="15">
+        <v>56</v>
+      </c>
+      <c r="E1229" s="15">
+        <v>16.2</v>
+      </c>
+      <c r="F1229" s="15">
+        <v>25</v>
+      </c>
+      <c r="G1229" s="16">
+        <v>109</v>
+      </c>
+      <c r="H1229" s="15">
+        <v>39</v>
+      </c>
+      <c r="I1229" s="16">
+        <v>112</v>
+      </c>
+      <c r="J1229" s="15">
+        <v>43</v>
+      </c>
+      <c r="K1229"/>
+      <c r="L1229"/>
+      <c r="M1229" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1229" s="11">
+        <v>1</v>
+      </c>
+      <c r="O1229" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:15">
+      <c r="A1230"/>
+      <c r="B1230"/>
+      <c r="C1230"/>
+      <c r="D1230"/>
+      <c r="E1230"/>
+      <c r="F1230"/>
+      <c r="G1230"/>
+      <c r="H1230"/>
+      <c r="I1230"/>
+      <c r="J1230"/>
+      <c r="K1230"/>
+      <c r="L1230"/>
+      <c r="M1230"/>
+      <c r="N1230"/>
+      <c r="O1230"/>
+    </row>
+    <row r="1231" spans="1:15">
+      <c r="A1231"/>
+      <c r="B1231"/>
+      <c r="C1231"/>
+      <c r="D1231"/>
+      <c r="E1231"/>
+      <c r="F1231"/>
+      <c r="G1231"/>
+      <c r="H1231"/>
+      <c r="I1231"/>
+      <c r="J1231"/>
+      <c r="K1231"/>
+      <c r="L1231"/>
+      <c r="M1231"/>
+      <c r="N1231"/>
+      <c r="O1231"/>
     </row>
   </sheetData>
   <sortState ref="B2:I17">
@@ -52532,7 +53258,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{b5cce397-cf48-46de-9f4c-f443b9a90bb4}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{d5fdf6f1-3d25-41ec-b71d-d6f36418c4b7}">
             <xm:f>NOT(ISERROR(SEARCH(#REF!,M61)))</xm:f>
             <xm:f>#REF!</xm:f>
             <x14:dxf>

--- a/train_data3.xlsx
+++ b/train_data3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="732">
   <si>
     <t>レースID</t>
   </si>
@@ -2198,6 +2198,18 @@
   </si>
   <si>
     <t>カズタンジャー</t>
+  </si>
+  <si>
+    <t>ディープモンスター</t>
+  </si>
+  <si>
+    <t>ショウナンラプンタ</t>
+  </si>
+  <si>
+    <t>レイニング</t>
+  </si>
+  <si>
+    <t>ダノンエアズロック</t>
   </si>
 </sst>
 </file>
@@ -3326,7 +3338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1231"/>
+  <dimension ref="A1:O1265"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" width="8.72222222222222" style="1"/>
@@ -53139,38 +53151,1494 @@
       </c>
     </row>
     <row r="1230" spans="1:15">
-      <c r="A1230"/>
-      <c r="B1230"/>
-      <c r="C1230"/>
-      <c r="D1230"/>
-      <c r="E1230"/>
-      <c r="F1230"/>
-      <c r="G1230"/>
-      <c r="H1230"/>
-      <c r="I1230"/>
-      <c r="J1230"/>
+      <c r="A1230" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1230" s="15">
+        <v>1</v>
+      </c>
+      <c r="C1230" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1230" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1230" s="15">
+        <v>23</v>
+      </c>
+      <c r="F1230" s="15">
+        <v>26</v>
+      </c>
+      <c r="G1230" s="16">
+        <v>96</v>
+      </c>
+      <c r="H1230" s="15">
+        <v>9</v>
+      </c>
+      <c r="I1230" s="16">
+        <v>104</v>
+      </c>
+      <c r="J1230" s="15">
+        <v>35</v>
+      </c>
       <c r="K1230"/>
       <c r="L1230"/>
       <c r="M1230"/>
-      <c r="N1230"/>
-      <c r="O1230"/>
+      <c r="N1230" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1230" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="1231" spans="1:15">
-      <c r="A1231"/>
-      <c r="B1231"/>
-      <c r="C1231"/>
-      <c r="D1231"/>
-      <c r="E1231"/>
-      <c r="F1231"/>
-      <c r="G1231"/>
-      <c r="H1231"/>
-      <c r="I1231"/>
-      <c r="J1231"/>
+      <c r="A1231" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1231" s="15">
+        <v>2</v>
+      </c>
+      <c r="C1231" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1231" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1231" s="15">
+        <v>12</v>
+      </c>
+      <c r="F1231" s="15">
+        <v>4</v>
+      </c>
+      <c r="G1231" s="16">
+        <v>116</v>
+      </c>
+      <c r="H1231" s="15">
+        <v>95</v>
+      </c>
+      <c r="I1231" s="16">
+        <v>90</v>
+      </c>
+      <c r="J1231" s="15">
+        <v>43</v>
+      </c>
       <c r="K1231"/>
       <c r="L1231"/>
       <c r="M1231"/>
-      <c r="N1231"/>
-      <c r="O1231"/>
+      <c r="N1231" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1231" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:15">
+      <c r="A1232" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1232" s="15">
+        <v>3</v>
+      </c>
+      <c r="C1232" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="D1232" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1232" s="15">
+        <v>27</v>
+      </c>
+      <c r="F1232" s="15">
+        <v>23</v>
+      </c>
+      <c r="G1232" s="16">
+        <v>114</v>
+      </c>
+      <c r="H1232" s="15">
+        <v>-99</v>
+      </c>
+      <c r="I1232" s="16">
+        <v>114</v>
+      </c>
+      <c r="J1232" s="15">
+        <v>-99</v>
+      </c>
+      <c r="K1232" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1232"/>
+      <c r="M1232"/>
+      <c r="N1232" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1232" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:15">
+      <c r="A1233" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1233" s="15">
+        <v>4</v>
+      </c>
+      <c r="C1233" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1233" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1233" s="15">
+        <v>38.9</v>
+      </c>
+      <c r="F1233" s="15">
+        <v>30</v>
+      </c>
+      <c r="G1233" s="16">
+        <v>113</v>
+      </c>
+      <c r="H1233" s="15">
+        <v>-5</v>
+      </c>
+      <c r="I1233" s="16">
+        <v>84</v>
+      </c>
+      <c r="J1233" s="15">
+        <v>18</v>
+      </c>
+      <c r="K1233"/>
+      <c r="L1233"/>
+      <c r="M1233"/>
+      <c r="N1233" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1233" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:15">
+      <c r="A1234" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1234" s="15">
+        <v>5</v>
+      </c>
+      <c r="C1234" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="D1234" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1234" s="15">
+        <v>4.4</v>
+      </c>
+      <c r="F1234" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1234" s="16">
+        <v>96</v>
+      </c>
+      <c r="H1234" s="15">
+        <v>-18</v>
+      </c>
+      <c r="I1234" s="16">
+        <v>109</v>
+      </c>
+      <c r="J1234" s="15">
+        <v>-65</v>
+      </c>
+      <c r="K1234"/>
+      <c r="L1234"/>
+      <c r="M1234"/>
+      <c r="N1234" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1234" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:15">
+      <c r="A1235" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1235" s="15">
+        <v>6</v>
+      </c>
+      <c r="C1235" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1235" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1235" s="15">
+        <v>33.1</v>
+      </c>
+      <c r="F1235" s="15">
+        <v>27</v>
+      </c>
+      <c r="G1235" s="16">
+        <v>114</v>
+      </c>
+      <c r="H1235" s="15">
+        <v>45</v>
+      </c>
+      <c r="I1235" s="16">
+        <v>108</v>
+      </c>
+      <c r="J1235" s="15">
+        <v>33</v>
+      </c>
+      <c r="K1235" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1235"/>
+      <c r="M1235"/>
+      <c r="N1235" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1235" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:15">
+      <c r="A1236" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1236" s="15">
+        <v>7</v>
+      </c>
+      <c r="C1236" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1236" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1236" s="15">
+        <v>4.8</v>
+      </c>
+      <c r="F1236" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1236" s="16">
+        <v>51</v>
+      </c>
+      <c r="H1236" s="15">
+        <v>-216</v>
+      </c>
+      <c r="I1236" s="16">
+        <v>92</v>
+      </c>
+      <c r="J1236" s="15">
+        <v>16</v>
+      </c>
+      <c r="K1236" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1236"/>
+      <c r="M1236" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1236" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1236" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:15">
+      <c r="A1237" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1237" s="15">
+        <v>8</v>
+      </c>
+      <c r="C1237" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1237" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1237" s="15">
+        <v>14.2</v>
+      </c>
+      <c r="F1237" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1237" s="16">
+        <v>82</v>
+      </c>
+      <c r="H1237" s="15">
+        <v>-109</v>
+      </c>
+      <c r="I1237" s="16">
+        <v>108</v>
+      </c>
+      <c r="J1237" s="15">
+        <v>52</v>
+      </c>
+      <c r="K1237"/>
+      <c r="L1237" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1237"/>
+      <c r="N1237" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1237" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:15">
+      <c r="A1238" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1238" s="15">
+        <v>9</v>
+      </c>
+      <c r="C1238" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1238" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1238" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="F1238" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1238" s="16">
+        <v>76</v>
+      </c>
+      <c r="H1238" s="15">
+        <v>-179</v>
+      </c>
+      <c r="I1238" s="16">
+        <v>110</v>
+      </c>
+      <c r="J1238" s="15">
+        <v>15</v>
+      </c>
+      <c r="K1238"/>
+      <c r="L1238"/>
+      <c r="M1238" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1238" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1238" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:15">
+      <c r="A1239" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1239" s="15">
+        <v>10</v>
+      </c>
+      <c r="C1239" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1239" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1239" s="15">
+        <v>9</v>
+      </c>
+      <c r="F1239" s="15">
+        <v>8</v>
+      </c>
+      <c r="G1239" s="16">
+        <v>87</v>
+      </c>
+      <c r="H1239" s="15">
+        <v>-82</v>
+      </c>
+      <c r="I1239" s="16">
+        <v>105</v>
+      </c>
+      <c r="J1239" s="15">
+        <v>-8</v>
+      </c>
+      <c r="K1239"/>
+      <c r="L1239"/>
+      <c r="M1239"/>
+      <c r="N1239" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1239" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:15">
+      <c r="A1240" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1240" s="15">
+        <v>11</v>
+      </c>
+      <c r="C1240" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1240" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1240" s="15">
+        <v>6.9</v>
+      </c>
+      <c r="F1240" s="15">
+        <v>10</v>
+      </c>
+      <c r="G1240" s="16">
+        <v>89</v>
+      </c>
+      <c r="H1240" s="15">
+        <v>-30</v>
+      </c>
+      <c r="I1240" s="16">
+        <v>98</v>
+      </c>
+      <c r="J1240" s="15">
+        <v>-103</v>
+      </c>
+      <c r="K1240"/>
+      <c r="L1240" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1240"/>
+      <c r="N1240" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1240" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:15">
+      <c r="A1241" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1241" s="15">
+        <v>12</v>
+      </c>
+      <c r="C1241" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1241" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1241" s="15">
+        <v>12.7</v>
+      </c>
+      <c r="F1241" s="15">
+        <v>11</v>
+      </c>
+      <c r="G1241" s="16">
+        <v>106</v>
+      </c>
+      <c r="H1241" s="15">
+        <v>-16</v>
+      </c>
+      <c r="I1241" s="16">
+        <v>15</v>
+      </c>
+      <c r="J1241" s="15">
+        <v>-967</v>
+      </c>
+      <c r="K1241"/>
+      <c r="L1241"/>
+      <c r="M1241" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1241" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1241" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:15">
+      <c r="A1242" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1242" s="15">
+        <v>13</v>
+      </c>
+      <c r="C1242" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1242" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1242" s="15">
+        <v>6.7</v>
+      </c>
+      <c r="F1242" s="15">
+        <v>2</v>
+      </c>
+      <c r="G1242" s="16">
+        <v>92</v>
+      </c>
+      <c r="H1242" s="15">
+        <v>-31</v>
+      </c>
+      <c r="I1242" s="16">
+        <v>88</v>
+      </c>
+      <c r="J1242" s="15">
+        <v>-43</v>
+      </c>
+      <c r="K1242"/>
+      <c r="L1242"/>
+      <c r="M1242"/>
+      <c r="N1242" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1242" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:15">
+      <c r="A1243" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1243" s="15">
+        <v>14</v>
+      </c>
+      <c r="C1243" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="D1243" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1243" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="F1243" s="15">
+        <v>13</v>
+      </c>
+      <c r="G1243" s="16">
+        <v>92</v>
+      </c>
+      <c r="H1243" s="15">
+        <v>14</v>
+      </c>
+      <c r="I1243" s="16">
+        <v>88</v>
+      </c>
+      <c r="J1243" s="15">
+        <v>-69</v>
+      </c>
+      <c r="K1243"/>
+      <c r="L1243"/>
+      <c r="M1243"/>
+      <c r="N1243" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1243" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:15">
+      <c r="A1244" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1244" s="15">
+        <v>15</v>
+      </c>
+      <c r="C1244" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1244" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1244" s="15">
+        <v>6</v>
+      </c>
+      <c r="F1244" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1244"/>
+      <c r="H1244"/>
+      <c r="I1244"/>
+      <c r="J1244"/>
+      <c r="K1244"/>
+      <c r="L1244"/>
+      <c r="M1244"/>
+      <c r="N1244" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1244" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:15">
+      <c r="A1245" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1245" s="15">
+        <v>16</v>
+      </c>
+      <c r="C1245" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="D1245" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1245" s="15">
+        <v>12.9</v>
+      </c>
+      <c r="F1245" s="15">
+        <v>15</v>
+      </c>
+      <c r="G1245" s="16">
+        <v>106</v>
+      </c>
+      <c r="H1245" s="15">
+        <v>35</v>
+      </c>
+      <c r="I1245" s="16">
+        <v>104</v>
+      </c>
+      <c r="J1245" s="15">
+        <v>19</v>
+      </c>
+      <c r="K1245"/>
+      <c r="L1245"/>
+      <c r="M1245"/>
+      <c r="N1245" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1245" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:15">
+      <c r="A1246" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1246" s="15">
+        <v>17</v>
+      </c>
+      <c r="C1246" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="D1246" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1246" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="F1246" s="15">
+        <v>10</v>
+      </c>
+      <c r="G1246" s="16">
+        <v>101</v>
+      </c>
+      <c r="H1246" s="15">
+        <v>5</v>
+      </c>
+      <c r="I1246" s="16">
+        <v>103</v>
+      </c>
+      <c r="J1246" s="15">
+        <v>72</v>
+      </c>
+      <c r="K1246"/>
+      <c r="L1246" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1246" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1246" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1246" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:15">
+      <c r="A1247" s="15">
+        <v>84</v>
+      </c>
+      <c r="B1247" s="15">
+        <v>18</v>
+      </c>
+      <c r="C1247" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1247" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1247" s="15">
+        <v>63.8</v>
+      </c>
+      <c r="F1247" s="15">
+        <v>43</v>
+      </c>
+      <c r="G1247" s="16">
+        <v>93</v>
+      </c>
+      <c r="H1247" s="15">
+        <v>4</v>
+      </c>
+      <c r="I1247" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1247" s="15">
+        <v>54</v>
+      </c>
+      <c r="K1247"/>
+      <c r="L1247"/>
+      <c r="M1247"/>
+      <c r="N1247" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1247" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:15">
+      <c r="A1248" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1248" s="15">
+        <v>1</v>
+      </c>
+      <c r="C1248" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1248" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1248" s="15">
+        <v>28.3</v>
+      </c>
+      <c r="F1248" s="15">
+        <v>26</v>
+      </c>
+      <c r="G1248" s="16">
+        <v>103</v>
+      </c>
+      <c r="H1248" s="15">
+        <v>28</v>
+      </c>
+      <c r="I1248" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1248" s="15">
+        <v>1</v>
+      </c>
+      <c r="K1248"/>
+      <c r="L1248"/>
+      <c r="M1248" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1248" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1248" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:15">
+      <c r="A1249" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1249" s="15">
+        <v>2</v>
+      </c>
+      <c r="C1249" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1249" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1249" s="15">
+        <v>58</v>
+      </c>
+      <c r="F1249" s="15">
+        <v>44</v>
+      </c>
+      <c r="G1249" s="16">
+        <v>104</v>
+      </c>
+      <c r="H1249" s="15">
+        <v>3</v>
+      </c>
+      <c r="I1249" s="16">
+        <v>110</v>
+      </c>
+      <c r="J1249" s="15">
+        <v>38</v>
+      </c>
+      <c r="K1249" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1249" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1249" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1249" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1249" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:15">
+      <c r="A1250" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1250" s="15">
+        <v>3</v>
+      </c>
+      <c r="C1250" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D1250" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1250" s="15">
+        <v>9.9</v>
+      </c>
+      <c r="F1250" s="15">
+        <v>14</v>
+      </c>
+      <c r="G1250" s="16">
+        <v>103</v>
+      </c>
+      <c r="H1250" s="15">
+        <v>7</v>
+      </c>
+      <c r="I1250" s="16">
+        <v>89</v>
+      </c>
+      <c r="J1250" s="15">
+        <v>-31</v>
+      </c>
+      <c r="K1250"/>
+      <c r="L1250"/>
+      <c r="M1250"/>
+      <c r="N1250" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1250" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:15">
+      <c r="A1251" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1251" s="15">
+        <v>4</v>
+      </c>
+      <c r="C1251" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D1251" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1251" s="15">
+        <v>46.9</v>
+      </c>
+      <c r="F1251" s="15">
+        <v>25</v>
+      </c>
+      <c r="G1251" s="16">
+        <v>113</v>
+      </c>
+      <c r="H1251" s="15">
+        <v>48</v>
+      </c>
+      <c r="I1251" s="16">
+        <v>110</v>
+      </c>
+      <c r="J1251" s="15">
+        <v>20</v>
+      </c>
+      <c r="K1251"/>
+      <c r="L1251"/>
+      <c r="M1251" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1251" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1251" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:15">
+      <c r="A1252" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1252" s="15">
+        <v>5</v>
+      </c>
+      <c r="C1252" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="D1252" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1252" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="F1252" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1252" s="16">
+        <v>101</v>
+      </c>
+      <c r="H1252" s="15">
+        <v>2</v>
+      </c>
+      <c r="I1252" s="16">
+        <v>89</v>
+      </c>
+      <c r="J1252" s="15">
+        <v>-29</v>
+      </c>
+      <c r="K1252"/>
+      <c r="L1252"/>
+      <c r="M1252"/>
+      <c r="N1252" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1252" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:15">
+      <c r="A1253" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1253" s="15">
+        <v>6</v>
+      </c>
+      <c r="C1253" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1253" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1253" s="15">
+        <v>44.7</v>
+      </c>
+      <c r="F1253" s="15">
+        <v>31</v>
+      </c>
+      <c r="G1253" s="16">
+        <v>90</v>
+      </c>
+      <c r="H1253" s="15">
+        <v>73</v>
+      </c>
+      <c r="I1253" s="16">
+        <v>104</v>
+      </c>
+      <c r="J1253" s="15">
+        <v>17</v>
+      </c>
+      <c r="K1253"/>
+      <c r="L1253" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1253"/>
+      <c r="N1253" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1253" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:15">
+      <c r="A1254" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1254" s="15">
+        <v>7</v>
+      </c>
+      <c r="C1254" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1254" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1254" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="F1254" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1254" s="16">
+        <v>90</v>
+      </c>
+      <c r="H1254" s="15">
+        <v>-96</v>
+      </c>
+      <c r="I1254" s="16">
+        <v>99</v>
+      </c>
+      <c r="J1254" s="15">
+        <v>-45</v>
+      </c>
+      <c r="K1254"/>
+      <c r="L1254"/>
+      <c r="M1254"/>
+      <c r="N1254" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1254" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:15">
+      <c r="A1255" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1255" s="15">
+        <v>8</v>
+      </c>
+      <c r="C1255" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1255" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1255" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="F1255" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1255" s="16">
+        <v>91</v>
+      </c>
+      <c r="H1255" s="15">
+        <v>2</v>
+      </c>
+      <c r="I1255" s="16">
+        <v>83</v>
+      </c>
+      <c r="J1255" s="15">
+        <v>-18</v>
+      </c>
+      <c r="K1255"/>
+      <c r="L1255"/>
+      <c r="M1255"/>
+      <c r="N1255" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1255" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:15">
+      <c r="A1256" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1256" s="15">
+        <v>9</v>
+      </c>
+      <c r="C1256" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D1256" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1256" s="15">
+        <v>20.3</v>
+      </c>
+      <c r="F1256" s="15">
+        <v>32</v>
+      </c>
+      <c r="G1256" s="16">
+        <v>97</v>
+      </c>
+      <c r="H1256" s="15">
+        <v>22</v>
+      </c>
+      <c r="I1256" s="16">
+        <v>106</v>
+      </c>
+      <c r="J1256" s="15">
+        <v>30</v>
+      </c>
+      <c r="K1256"/>
+      <c r="L1256" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1256"/>
+      <c r="N1256" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1256" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:15">
+      <c r="A1257" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1257" s="15">
+        <v>10</v>
+      </c>
+      <c r="C1257" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1257" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1257" s="15">
+        <v>12.1</v>
+      </c>
+      <c r="F1257" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1257" s="16">
+        <v>85</v>
+      </c>
+      <c r="H1257" s="15">
+        <v>-32</v>
+      </c>
+      <c r="I1257" s="16">
+        <v>94</v>
+      </c>
+      <c r="J1257" s="15">
+        <v>76</v>
+      </c>
+      <c r="K1257"/>
+      <c r="L1257"/>
+      <c r="M1257"/>
+      <c r="N1257" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1257" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:15">
+      <c r="A1258" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1258" s="15">
+        <v>11</v>
+      </c>
+      <c r="C1258" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1258" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1258" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="F1258" s="15">
+        <v>14</v>
+      </c>
+      <c r="G1258" s="16">
+        <v>54</v>
+      </c>
+      <c r="H1258" s="15">
+        <v>-395</v>
+      </c>
+      <c r="I1258" s="16">
+        <v>104</v>
+      </c>
+      <c r="J1258" s="15">
+        <v>-6</v>
+      </c>
+      <c r="K1258"/>
+      <c r="L1258"/>
+      <c r="M1258"/>
+      <c r="N1258" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1258" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:15">
+      <c r="A1259" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1259" s="15">
+        <v>12</v>
+      </c>
+      <c r="C1259" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1259" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1259" s="15">
+        <v>9.5</v>
+      </c>
+      <c r="F1259" s="15">
+        <v>25</v>
+      </c>
+      <c r="G1259" s="16">
+        <v>87</v>
+      </c>
+      <c r="H1259" s="15">
+        <v>-4</v>
+      </c>
+      <c r="I1259" s="16">
+        <v>91</v>
+      </c>
+      <c r="J1259" s="15">
+        <v>24</v>
+      </c>
+      <c r="K1259"/>
+      <c r="L1259" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1259"/>
+      <c r="N1259" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1259" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:15">
+      <c r="A1260" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1260" s="15">
+        <v>13</v>
+      </c>
+      <c r="C1260" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1260" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1260" s="15">
+        <v>13.1</v>
+      </c>
+      <c r="F1260" s="15">
+        <v>16</v>
+      </c>
+      <c r="G1260" s="16">
+        <v>97</v>
+      </c>
+      <c r="H1260" s="15">
+        <v>-23</v>
+      </c>
+      <c r="I1260" s="16">
+        <v>102</v>
+      </c>
+      <c r="J1260" s="15">
+        <v>-60</v>
+      </c>
+      <c r="K1260" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1260" s="15">
+        <v>1</v>
+      </c>
+      <c r="M1260" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1260" s="15">
+        <v>1</v>
+      </c>
+      <c r="O1260" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:15">
+      <c r="A1261" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1261" s="15">
+        <v>14</v>
+      </c>
+      <c r="C1261" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="D1261" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1261" s="15">
+        <v>12.8</v>
+      </c>
+      <c r="F1261" s="15">
+        <v>24</v>
+      </c>
+      <c r="G1261" s="16">
+        <v>89</v>
+      </c>
+      <c r="H1261" s="15">
+        <v>14</v>
+      </c>
+      <c r="I1261" s="16">
+        <v>103</v>
+      </c>
+      <c r="J1261" s="15">
+        <v>31</v>
+      </c>
+      <c r="K1261" s="15">
+        <v>1</v>
+      </c>
+      <c r="L1261"/>
+      <c r="M1261"/>
+      <c r="N1261" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1261" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:15">
+      <c r="A1262" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1262" s="15">
+        <v>15</v>
+      </c>
+      <c r="C1262" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1262" s="15">
+        <v>58</v>
+      </c>
+      <c r="E1262" s="15">
+        <v>6.6</v>
+      </c>
+      <c r="F1262" s="15">
+        <v>10</v>
+      </c>
+      <c r="G1262" s="16">
+        <v>93</v>
+      </c>
+      <c r="H1262" s="15">
+        <v>-12</v>
+      </c>
+      <c r="I1262" s="16">
+        <v>104</v>
+      </c>
+      <c r="J1262" s="15">
+        <v>-6</v>
+      </c>
+      <c r="K1262"/>
+      <c r="L1262"/>
+      <c r="M1262"/>
+      <c r="N1262" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1262" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:15">
+      <c r="A1263" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1263" s="15">
+        <v>16</v>
+      </c>
+      <c r="C1263" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1263" s="15">
+        <v>55</v>
+      </c>
+      <c r="E1263" s="15">
+        <v>13.7</v>
+      </c>
+      <c r="F1263" s="15">
+        <v>20</v>
+      </c>
+      <c r="G1263" s="16">
+        <v>105</v>
+      </c>
+      <c r="H1263" s="15">
+        <v>57</v>
+      </c>
+      <c r="I1263" s="16">
+        <v>100</v>
+      </c>
+      <c r="J1263" s="15">
+        <v>-79</v>
+      </c>
+      <c r="K1263"/>
+      <c r="L1263"/>
+      <c r="M1263"/>
+      <c r="N1263" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1263" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:15">
+      <c r="A1264" s="15">
+        <v>85</v>
+      </c>
+      <c r="B1264" s="15">
+        <v>17</v>
+      </c>
+      <c r="C1264" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1264" s="15">
+        <v>57</v>
+      </c>
+      <c r="E1264" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="F1264" s="15">
+        <v>17</v>
+      </c>
+      <c r="G1264" s="16">
+        <v>91</v>
+      </c>
+      <c r="H1264" s="15">
+        <v>23</v>
+      </c>
+      <c r="I1264" s="16">
+        <v>100</v>
+      </c>
+      <c r="J1264" s="15">
+        <v>22</v>
+      </c>
+      <c r="K1264"/>
+      <c r="L1264"/>
+      <c r="M1264" s="15">
+        <v>1</v>
+      </c>
+      <c r="N1264" s="15">
+        <v>0</v>
+      </c>
+      <c r="O1264" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:15">
+      <c r="A1265"/>
+      <c r="B1265"/>
+      <c r="C1265"/>
+      <c r="D1265"/>
+      <c r="E1265"/>
+      <c r="F1265"/>
+      <c r="G1265"/>
+      <c r="H1265"/>
+      <c r="I1265"/>
+      <c r="J1265"/>
+      <c r="K1265"/>
+      <c r="L1265"/>
+      <c r="M1265"/>
+      <c r="N1265"/>
+      <c r="O1265"/>
     </row>
   </sheetData>
   <sortState ref="B2:I17">
@@ -53258,7 +54726,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{d5fdf6f1-3d25-41ec-b71d-d6f36418c4b7}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{ab90c351-4f5c-4951-995d-165805b339ed}">
             <xm:f>NOT(ISERROR(SEARCH(#REF!,M61)))</xm:f>
             <xm:f>#REF!</xm:f>
             <x14:dxf>
